--- a/data/graduation_requirements.xlsx
+++ b/data/graduation_requirements.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20343"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seung\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E97D17-63C4-4A7A-A9EE-1F2F7D5016DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540018D3-D6FF-408E-90F2-1F3C8F0F28E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$868</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1036</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="82">
   <si>
     <t>전공명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -235,10 +235,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>정보보안전공(평캠)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>제품공간디자인전공(평캠)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -316,6 +312,10 @@
   </si>
   <si>
     <t>컴퓨터공학전공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정보보안전공</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -644,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M868"/>
+  <dimension ref="A1:M1036"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -670,7 +670,7 @@
         <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>58</v>
@@ -682,7 +682,7 @@
         <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>44</v>
@@ -755,7 +755,7 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>2020</v>
@@ -822,10 +822,10 @@
         <v>2020</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G6">
         <v>36</v>
@@ -929,7 +929,7 @@
         <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10">
         <v>2020</v>
@@ -1016,7 +1016,7 @@
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13">
         <v>2020</v>
@@ -1045,7 +1045,7 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14">
         <v>2020</v>
@@ -1219,7 +1219,7 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C20">
         <v>2020</v>
@@ -1306,7 +1306,7 @@
         <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23">
         <v>2020</v>
@@ -1654,7 +1654,7 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C35">
         <v>2021</v>
@@ -1779,10 +1779,10 @@
         <v>2021</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F39">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G39">
         <v>36</v>
@@ -1915,7 +1915,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C44">
         <v>2021</v>
@@ -2031,7 +2031,7 @@
         <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C48">
         <v>2021</v>
@@ -2060,7 +2060,7 @@
         <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C49">
         <v>2021</v>
@@ -2234,7 +2234,7 @@
         <v>41</v>
       </c>
       <c r="B55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C55">
         <v>2021</v>
@@ -2321,7 +2321,7 @@
         <v>41</v>
       </c>
       <c r="B58" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>2021</v>
@@ -2669,7 +2669,7 @@
         <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C70">
         <v>2022</v>
@@ -2794,10 +2794,10 @@
         <v>2022</v>
       </c>
       <c r="E74">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F74">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G74">
         <v>36</v>
@@ -2930,7 +2930,7 @@
         <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C79">
         <v>2022</v>
@@ -3046,7 +3046,7 @@
         <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C83">
         <v>2022</v>
@@ -3075,7 +3075,7 @@
         <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C84">
         <v>2022</v>
@@ -3336,7 +3336,7 @@
         <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C93">
         <v>2022</v>
@@ -3684,7 +3684,7 @@
         <v>41</v>
       </c>
       <c r="B105" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C105">
         <v>2023</v>
@@ -3838,10 +3838,10 @@
         <v>2023</v>
       </c>
       <c r="E110">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F110">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G110">
         <v>36</v>
@@ -3974,7 +3974,7 @@
         <v>41</v>
       </c>
       <c r="B115" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C115">
         <v>2023</v>
@@ -4380,7 +4380,7 @@
         <v>41</v>
       </c>
       <c r="B129" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C129">
         <v>2023</v>
@@ -4467,7 +4467,7 @@
         <v>41</v>
       </c>
       <c r="B132" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C132">
         <v>2023</v>
@@ -4641,7 +4641,7 @@
         <v>41</v>
       </c>
       <c r="B138" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C138">
         <v>2023</v>
@@ -4728,7 +4728,7 @@
         <v>41</v>
       </c>
       <c r="B141" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C141">
         <v>2023</v>
@@ -4757,7 +4757,7 @@
         <v>41</v>
       </c>
       <c r="B142" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C142">
         <v>2023</v>
@@ -4786,7 +4786,7 @@
         <v>41</v>
       </c>
       <c r="B143" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C143">
         <v>2023</v>
@@ -4815,7 +4815,7 @@
         <v>41</v>
       </c>
       <c r="B144" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C144">
         <v>2023</v>
@@ -4873,7 +4873,7 @@
         <v>41</v>
       </c>
       <c r="B146" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C146">
         <v>2023</v>
@@ -4902,7 +4902,7 @@
         <v>41</v>
       </c>
       <c r="B147" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C147">
         <v>2023</v>
@@ -4931,7 +4931,7 @@
         <v>41</v>
       </c>
       <c r="B148" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C148">
         <v>2023</v>
@@ -4989,7 +4989,7 @@
         <v>41</v>
       </c>
       <c r="B150" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C150">
         <v>2023</v>
@@ -5143,10 +5143,10 @@
         <v>2024</v>
       </c>
       <c r="E155">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F155">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G155">
         <v>36</v>
@@ -5627,7 +5627,7 @@
         <v>41</v>
       </c>
       <c r="B172" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C172">
         <v>2024</v>
@@ -5714,7 +5714,7 @@
         <v>41</v>
       </c>
       <c r="B175" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C175">
         <v>2024</v>
@@ -5888,7 +5888,7 @@
         <v>41</v>
       </c>
       <c r="B181" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C181">
         <v>2024</v>
@@ -5975,7 +5975,7 @@
         <v>41</v>
       </c>
       <c r="B184" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C184">
         <v>2024</v>
@@ -6004,7 +6004,7 @@
         <v>41</v>
       </c>
       <c r="B185" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C185">
         <v>2024</v>
@@ -6033,7 +6033,7 @@
         <v>41</v>
       </c>
       <c r="B186" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C186">
         <v>2024</v>
@@ -6062,7 +6062,7 @@
         <v>41</v>
       </c>
       <c r="B187" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C187">
         <v>2024</v>
@@ -6091,7 +6091,7 @@
         <v>41</v>
       </c>
       <c r="B188" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C188">
         <v>2024</v>
@@ -6120,7 +6120,7 @@
         <v>41</v>
       </c>
       <c r="B189" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C189">
         <v>2024</v>
@@ -6149,7 +6149,7 @@
         <v>41</v>
       </c>
       <c r="B190" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C190">
         <v>2024</v>
@@ -6178,7 +6178,7 @@
         <v>41</v>
       </c>
       <c r="B191" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C191">
         <v>2024</v>
@@ -6207,7 +6207,7 @@
         <v>41</v>
       </c>
       <c r="B192" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C192">
         <v>2024</v>
@@ -6236,7 +6236,7 @@
         <v>41</v>
       </c>
       <c r="B193" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C193">
         <v>2024</v>
@@ -6564,10 +6564,10 @@
         <v>2025</v>
       </c>
       <c r="E204">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F204">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G204">
         <v>36</v>
@@ -7019,7 +7019,7 @@
         <v>41</v>
       </c>
       <c r="B220" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C220">
         <v>2025</v>
@@ -7077,7 +7077,7 @@
         <v>41</v>
       </c>
       <c r="B222" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C222">
         <v>2025</v>
@@ -7367,7 +7367,7 @@
         <v>41</v>
       </c>
       <c r="B232" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C232">
         <v>2025</v>
@@ -7396,7 +7396,7 @@
         <v>41</v>
       </c>
       <c r="B233" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C233">
         <v>2025</v>
@@ -7425,7 +7425,7 @@
         <v>41</v>
       </c>
       <c r="B234" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C234">
         <v>2025</v>
@@ -7454,7 +7454,7 @@
         <v>41</v>
       </c>
       <c r="B235" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C235">
         <v>2025</v>
@@ -7483,7 +7483,7 @@
         <v>41</v>
       </c>
       <c r="B236" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C236">
         <v>2025</v>
@@ -7512,7 +7512,7 @@
         <v>41</v>
       </c>
       <c r="B237" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C237">
         <v>2025</v>
@@ -7541,7 +7541,7 @@
         <v>41</v>
       </c>
       <c r="B238" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C238">
         <v>2025</v>
@@ -7570,7 +7570,7 @@
         <v>41</v>
       </c>
       <c r="B239" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C239">
         <v>2025</v>
@@ -7599,7 +7599,7 @@
         <v>41</v>
       </c>
       <c r="B240" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C240">
         <v>2025</v>
@@ -7628,7 +7628,7 @@
         <v>41</v>
       </c>
       <c r="B241" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C241">
         <v>2025</v>
@@ -7657,7 +7657,7 @@
         <v>41</v>
       </c>
       <c r="B242" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C242">
         <v>2025</v>
@@ -7910,7 +7910,7 @@
         <v>43</v>
       </c>
       <c r="B251" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C251">
         <v>2020</v>
@@ -7969,11 +7969,11 @@
         <v>2020</v>
       </c>
       <c r="E253">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F253">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G253">
         <f t="shared" si="1"/>
@@ -8060,7 +8060,7 @@
         <v>43</v>
       </c>
       <c r="B257" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C257">
         <v>2020</v>
@@ -8135,7 +8135,7 @@
         <v>43</v>
       </c>
       <c r="B260" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C260">
         <v>2020</v>
@@ -8160,7 +8160,7 @@
         <v>43</v>
       </c>
       <c r="B261" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C261">
         <v>2020</v>
@@ -8310,7 +8310,7 @@
         <v>43</v>
       </c>
       <c r="B267" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C267">
         <v>2020</v>
@@ -8385,7 +8385,7 @@
         <v>43</v>
       </c>
       <c r="B270" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C270">
         <v>2020</v>
@@ -8685,7 +8685,7 @@
         <v>43</v>
       </c>
       <c r="B282" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C282">
         <v>2021</v>
@@ -8794,11 +8794,11 @@
         <v>2021</v>
       </c>
       <c r="E286">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F286">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G286">
         <f t="shared" si="1"/>
@@ -8910,7 +8910,7 @@
         <v>43</v>
       </c>
       <c r="B291" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C291">
         <v>2021</v>
@@ -9010,7 +9010,7 @@
         <v>43</v>
       </c>
       <c r="B295" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C295">
         <v>2021</v>
@@ -9035,7 +9035,7 @@
         <v>43</v>
       </c>
       <c r="B296" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C296">
         <v>2021</v>
@@ -9185,7 +9185,7 @@
         <v>43</v>
       </c>
       <c r="B302" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C302">
         <v>2021</v>
@@ -9260,7 +9260,7 @@
         <v>43</v>
       </c>
       <c r="B305" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C305">
         <v>2021</v>
@@ -9560,7 +9560,7 @@
         <v>43</v>
       </c>
       <c r="B317" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C317">
         <v>2022</v>
@@ -9669,11 +9669,11 @@
         <v>2022</v>
       </c>
       <c r="E321">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F321">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G321">
         <f t="shared" si="3"/>
@@ -9785,7 +9785,7 @@
         <v>43</v>
       </c>
       <c r="B326" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C326">
         <v>2022</v>
@@ -9885,7 +9885,7 @@
         <v>43</v>
       </c>
       <c r="B330" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C330">
         <v>2022</v>
@@ -9910,7 +9910,7 @@
         <v>43</v>
       </c>
       <c r="B331" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C331">
         <v>2022</v>
@@ -10135,7 +10135,7 @@
         <v>43</v>
       </c>
       <c r="B340" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C340">
         <v>2022</v>
@@ -10435,7 +10435,7 @@
         <v>43</v>
       </c>
       <c r="B352" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C352">
         <v>2023</v>
@@ -10569,11 +10569,11 @@
         <v>2023</v>
       </c>
       <c r="E357">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F357">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G357">
         <f t="shared" si="3"/>
@@ -10685,7 +10685,7 @@
         <v>43</v>
       </c>
       <c r="B362" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C362">
         <v>2023</v>
@@ -11035,7 +11035,7 @@
         <v>43</v>
       </c>
       <c r="B376" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C376">
         <v>2023</v>
@@ -11110,7 +11110,7 @@
         <v>43</v>
       </c>
       <c r="B379" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C379">
         <v>2023</v>
@@ -11260,7 +11260,7 @@
         <v>43</v>
       </c>
       <c r="B385" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C385">
         <v>2023</v>
@@ -11335,7 +11335,7 @@
         <v>43</v>
       </c>
       <c r="B388" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C388">
         <v>2023</v>
@@ -11360,7 +11360,7 @@
         <v>43</v>
       </c>
       <c r="B389" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C389">
         <v>2023</v>
@@ -11385,7 +11385,7 @@
         <v>43</v>
       </c>
       <c r="B390" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C390">
         <v>2023</v>
@@ -11410,7 +11410,7 @@
         <v>43</v>
       </c>
       <c r="B391" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C391">
         <v>2023</v>
@@ -11460,7 +11460,7 @@
         <v>43</v>
       </c>
       <c r="B393" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C393">
         <v>2023</v>
@@ -11485,7 +11485,7 @@
         <v>43</v>
       </c>
       <c r="B394" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C394">
         <v>2023</v>
@@ -11510,7 +11510,7 @@
         <v>43</v>
       </c>
       <c r="B395" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C395">
         <v>2023</v>
@@ -11560,7 +11560,7 @@
         <v>43</v>
       </c>
       <c r="B397" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C397">
         <v>2023</v>
@@ -11694,11 +11694,11 @@
         <v>2024</v>
       </c>
       <c r="E402">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F402">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G402">
         <f t="shared" si="5"/>
@@ -12110,7 +12110,7 @@
         <v>43</v>
       </c>
       <c r="B419" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C419">
         <v>2024</v>
@@ -12185,7 +12185,7 @@
         <v>43</v>
       </c>
       <c r="B422" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C422">
         <v>2024</v>
@@ -12335,7 +12335,7 @@
         <v>43</v>
       </c>
       <c r="B428" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C428">
         <v>2024</v>
@@ -12410,7 +12410,7 @@
         <v>43</v>
       </c>
       <c r="B431" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C431">
         <v>2024</v>
@@ -12435,7 +12435,7 @@
         <v>43</v>
       </c>
       <c r="B432" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C432">
         <v>2024</v>
@@ -12460,7 +12460,7 @@
         <v>43</v>
       </c>
       <c r="B433" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C433">
         <v>2024</v>
@@ -12485,7 +12485,7 @@
         <v>43</v>
       </c>
       <c r="B434" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C434">
         <v>2024</v>
@@ -12510,7 +12510,7 @@
         <v>43</v>
       </c>
       <c r="B435" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C435">
         <v>2024</v>
@@ -12535,7 +12535,7 @@
         <v>43</v>
       </c>
       <c r="B436" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C436">
         <v>2024</v>
@@ -12560,7 +12560,7 @@
         <v>43</v>
       </c>
       <c r="B437" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C437">
         <v>2024</v>
@@ -12585,7 +12585,7 @@
         <v>43</v>
       </c>
       <c r="B438" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C438">
         <v>2024</v>
@@ -12610,7 +12610,7 @@
         <v>43</v>
       </c>
       <c r="B439" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C439">
         <v>2024</v>
@@ -12635,7 +12635,7 @@
         <v>43</v>
       </c>
       <c r="B440" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C440">
         <v>2024</v>
@@ -12919,11 +12919,11 @@
         <v>2025</v>
       </c>
       <c r="E451">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F451">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G451">
         <f t="shared" si="7"/>
@@ -13310,7 +13310,7 @@
         <v>43</v>
       </c>
       <c r="B467" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C467">
         <v>2025</v>
@@ -13360,7 +13360,7 @@
         <v>43</v>
       </c>
       <c r="B469" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C469">
         <v>2025</v>
@@ -13609,7 +13609,7 @@
         <v>43</v>
       </c>
       <c r="B479" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C479">
         <v>2025</v>
@@ -13634,7 +13634,7 @@
         <v>43</v>
       </c>
       <c r="B480" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C480">
         <v>2025</v>
@@ -13659,7 +13659,7 @@
         <v>43</v>
       </c>
       <c r="B481" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C481">
         <v>2025</v>
@@ -13684,7 +13684,7 @@
         <v>43</v>
       </c>
       <c r="B482" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C482">
         <v>2025</v>
@@ -13709,7 +13709,7 @@
         <v>43</v>
       </c>
       <c r="B483" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C483">
         <v>2025</v>
@@ -13734,7 +13734,7 @@
         <v>43</v>
       </c>
       <c r="B484" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C484">
         <v>2025</v>
@@ -13759,7 +13759,7 @@
         <v>43</v>
       </c>
       <c r="B485" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C485">
         <v>2025</v>
@@ -13784,7 +13784,7 @@
         <v>43</v>
       </c>
       <c r="B486" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C486">
         <v>2025</v>
@@ -13809,7 +13809,7 @@
         <v>43</v>
       </c>
       <c r="B487" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C487">
         <v>2025</v>
@@ -13834,7 +13834,7 @@
         <v>43</v>
       </c>
       <c r="B488" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C488">
         <v>2025</v>
@@ -13859,7 +13859,7 @@
         <v>43</v>
       </c>
       <c r="B489" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C489">
         <v>2025</v>
@@ -15963,7 +15963,7 @@
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B580" t="s">
         <v>2</v>
@@ -15986,7 +15986,7 @@
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B581" t="s">
         <v>48</v>
@@ -16009,10 +16009,10 @@
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B582" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C582">
         <v>2020</v>
@@ -16032,7 +16032,7 @@
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B583" t="s">
         <v>4</v>
@@ -16055,7 +16055,7 @@
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B584" t="s">
         <v>47</v>
@@ -16078,7 +16078,7 @@
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B585" t="s">
         <v>6</v>
@@ -16101,7 +16101,7 @@
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B586" t="s">
         <v>40</v>
@@ -16124,7 +16124,7 @@
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B587" t="s">
         <v>7</v>
@@ -16147,10 +16147,10 @@
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
+        <v>74</v>
+      </c>
+      <c r="B588" t="s">
         <v>75</v>
-      </c>
-      <c r="B588" t="s">
-        <v>76</v>
       </c>
       <c r="C588">
         <v>2020</v>
@@ -16170,7 +16170,7 @@
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B589" t="s">
         <v>8</v>
@@ -16193,7 +16193,7 @@
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B590" t="s">
         <v>9</v>
@@ -16216,10 +16216,10 @@
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B591" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C591">
         <v>2020</v>
@@ -16239,10 +16239,10 @@
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B592" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C592">
         <v>2020</v>
@@ -16262,7 +16262,7 @@
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B593" t="s">
         <v>10</v>
@@ -16285,7 +16285,7 @@
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B594" t="s">
         <v>11</v>
@@ -16308,7 +16308,7 @@
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B595" t="s">
         <v>12</v>
@@ -16331,7 +16331,7 @@
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B596" t="s">
         <v>13</v>
@@ -16354,7 +16354,7 @@
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B597" t="s">
         <v>28</v>
@@ -16377,10 +16377,10 @@
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B598" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C598">
         <v>2020</v>
@@ -16400,7 +16400,7 @@
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B599" t="s">
         <v>14</v>
@@ -16423,7 +16423,7 @@
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B600" t="s">
         <v>15</v>
@@ -16446,10 +16446,10 @@
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B601" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C601">
         <v>2020</v>
@@ -16469,7 +16469,7 @@
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B602" t="s">
         <v>16</v>
@@ -16492,7 +16492,7 @@
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B603" t="s">
         <v>17</v>
@@ -16515,7 +16515,7 @@
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B604" t="s">
         <v>18</v>
@@ -16538,7 +16538,7 @@
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B605" t="s">
         <v>19</v>
@@ -16561,7 +16561,7 @@
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B606" t="s">
         <v>20</v>
@@ -16584,7 +16584,7 @@
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B607" t="s">
         <v>21</v>
@@ -16607,7 +16607,7 @@
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B608" t="s">
         <v>37</v>
@@ -16630,7 +16630,7 @@
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B609" t="s">
         <v>22</v>
@@ -16653,7 +16653,7 @@
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B610" t="s">
         <v>23</v>
@@ -16676,7 +16676,7 @@
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B611" t="s">
         <v>2</v>
@@ -16699,7 +16699,7 @@
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B612" t="s">
         <v>3</v>
@@ -16722,10 +16722,10 @@
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B613" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C613">
         <v>2021</v>
@@ -16745,7 +16745,7 @@
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B614" t="s">
         <v>24</v>
@@ -16768,7 +16768,7 @@
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B615" t="s">
         <v>25</v>
@@ -16791,7 +16791,7 @@
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B616" t="s">
         <v>4</v>
@@ -16814,7 +16814,7 @@
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B617" t="s">
         <v>5</v>
@@ -16837,7 +16837,7 @@
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B618" t="s">
         <v>26</v>
@@ -16860,7 +16860,7 @@
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B619" t="s">
         <v>6</v>
@@ -16883,7 +16883,7 @@
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B620" t="s">
         <v>40</v>
@@ -16906,7 +16906,7 @@
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B621" t="s">
         <v>7</v>
@@ -16929,10 +16929,10 @@
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
+        <v>74</v>
+      </c>
+      <c r="B622" t="s">
         <v>75</v>
-      </c>
-      <c r="B622" t="s">
-        <v>76</v>
       </c>
       <c r="C622">
         <v>2021</v>
@@ -16952,7 +16952,7 @@
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B623" t="s">
         <v>27</v>
@@ -16975,7 +16975,7 @@
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B624" t="s">
         <v>8</v>
@@ -16998,7 +16998,7 @@
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B625" t="s">
         <v>9</v>
@@ -17021,10 +17021,10 @@
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B626" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C626">
         <v>2021</v>
@@ -17044,10 +17044,10 @@
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B627" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C627">
         <v>2021</v>
@@ -17067,7 +17067,7 @@
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B628" t="s">
         <v>10</v>
@@ -17090,7 +17090,7 @@
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B629" t="s">
         <v>11</v>
@@ -17113,7 +17113,7 @@
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B630" t="s">
         <v>12</v>
@@ -17136,7 +17136,7 @@
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B631" t="s">
         <v>13</v>
@@ -17159,7 +17159,7 @@
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B632" t="s">
         <v>28</v>
@@ -17182,10 +17182,10 @@
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B633" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C633">
         <v>2021</v>
@@ -17205,7 +17205,7 @@
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B634" t="s">
         <v>14</v>
@@ -17228,7 +17228,7 @@
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B635" t="s">
         <v>15</v>
@@ -17251,10 +17251,10 @@
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B636" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C636">
         <v>2021</v>
@@ -17274,7 +17274,7 @@
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B637" t="s">
         <v>16</v>
@@ -17297,7 +17297,7 @@
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B638" t="s">
         <v>17</v>
@@ -17320,7 +17320,7 @@
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B639" t="s">
         <v>18</v>
@@ -17343,7 +17343,7 @@
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B640" t="s">
         <v>19</v>
@@ -17366,7 +17366,7 @@
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B641" t="s">
         <v>20</v>
@@ -17389,7 +17389,7 @@
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B642" t="s">
         <v>21</v>
@@ -17412,7 +17412,7 @@
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B643" t="s">
         <v>37</v>
@@ -17435,7 +17435,7 @@
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B644" t="s">
         <v>22</v>
@@ -17458,7 +17458,7 @@
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B645" t="s">
         <v>23</v>
@@ -17481,7 +17481,7 @@
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B646" t="s">
         <v>2</v>
@@ -17504,7 +17504,7 @@
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B647" t="s">
         <v>3</v>
@@ -17527,10 +17527,10 @@
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B648" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C648">
         <v>2022</v>
@@ -17550,7 +17550,7 @@
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B649" t="s">
         <v>24</v>
@@ -17573,7 +17573,7 @@
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B650" t="s">
         <v>25</v>
@@ -17596,7 +17596,7 @@
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B651" t="s">
         <v>4</v>
@@ -17619,7 +17619,7 @@
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B652" t="s">
         <v>5</v>
@@ -17642,7 +17642,7 @@
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B653" t="s">
         <v>26</v>
@@ -17665,7 +17665,7 @@
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B654" t="s">
         <v>6</v>
@@ -17688,7 +17688,7 @@
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B655" t="s">
         <v>40</v>
@@ -17711,7 +17711,7 @@
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B656" t="s">
         <v>7</v>
@@ -17734,10 +17734,10 @@
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
+        <v>74</v>
+      </c>
+      <c r="B657" t="s">
         <v>75</v>
-      </c>
-      <c r="B657" t="s">
-        <v>76</v>
       </c>
       <c r="C657">
         <v>2022</v>
@@ -17757,7 +17757,7 @@
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B658" t="s">
         <v>27</v>
@@ -17780,7 +17780,7 @@
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B659" t="s">
         <v>8</v>
@@ -17803,7 +17803,7 @@
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B660" t="s">
         <v>9</v>
@@ -17826,10 +17826,10 @@
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B661" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C661">
         <v>2022</v>
@@ -17849,10 +17849,10 @@
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B662" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C662">
         <v>2022</v>
@@ -17872,7 +17872,7 @@
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B663" t="s">
         <v>10</v>
@@ -17895,7 +17895,7 @@
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B664" t="s">
         <v>11</v>
@@ -17918,7 +17918,7 @@
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B665" t="s">
         <v>12</v>
@@ -17941,7 +17941,7 @@
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B666" t="s">
         <v>13</v>
@@ -17964,7 +17964,7 @@
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B667" t="s">
         <v>28</v>
@@ -17987,7 +17987,7 @@
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B668" t="s">
         <v>29</v>
@@ -18010,7 +18010,7 @@
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B669" t="s">
         <v>14</v>
@@ -18033,7 +18033,7 @@
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B670" t="s">
         <v>15</v>
@@ -18056,10 +18056,10 @@
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B671" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C671">
         <v>2022</v>
@@ -18079,7 +18079,7 @@
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B672" t="s">
         <v>16</v>
@@ -18102,7 +18102,7 @@
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B673" t="s">
         <v>17</v>
@@ -18125,7 +18125,7 @@
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B674" t="s">
         <v>18</v>
@@ -18148,7 +18148,7 @@
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B675" t="s">
         <v>19</v>
@@ -18171,7 +18171,7 @@
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B676" t="s">
         <v>20</v>
@@ -18194,7 +18194,7 @@
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B677" t="s">
         <v>21</v>
@@ -18217,7 +18217,7 @@
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B678" t="s">
         <v>37</v>
@@ -18240,7 +18240,7 @@
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B679" t="s">
         <v>22</v>
@@ -18263,7 +18263,7 @@
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B680" t="s">
         <v>23</v>
@@ -18286,7 +18286,7 @@
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B681" t="s">
         <v>2</v>
@@ -18309,7 +18309,7 @@
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B682" t="s">
         <v>3</v>
@@ -18332,10 +18332,10 @@
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B683" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C683">
         <v>2023</v>
@@ -18355,7 +18355,7 @@
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B684" t="s">
         <v>24</v>
@@ -18378,7 +18378,7 @@
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B685" t="s">
         <v>25</v>
@@ -18401,7 +18401,7 @@
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B686" t="s">
         <v>30</v>
@@ -18424,7 +18424,7 @@
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B687" t="s">
         <v>4</v>
@@ -18447,7 +18447,7 @@
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B688" t="s">
         <v>5</v>
@@ -18470,7 +18470,7 @@
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B689" t="s">
         <v>26</v>
@@ -18493,7 +18493,7 @@
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B690" t="s">
         <v>6</v>
@@ -18516,7 +18516,7 @@
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B691" t="s">
         <v>40</v>
@@ -18539,7 +18539,7 @@
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B692" t="s">
         <v>7</v>
@@ -18562,10 +18562,10 @@
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
+        <v>74</v>
+      </c>
+      <c r="B693" t="s">
         <v>75</v>
-      </c>
-      <c r="B693" t="s">
-        <v>76</v>
       </c>
       <c r="C693">
         <v>2023</v>
@@ -18585,7 +18585,7 @@
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B694" t="s">
         <v>27</v>
@@ -18608,7 +18608,7 @@
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B695" t="s">
         <v>8</v>
@@ -18631,7 +18631,7 @@
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B696" t="s">
         <v>9</v>
@@ -18654,7 +18654,7 @@
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B697" t="s">
         <v>31</v>
@@ -18677,7 +18677,7 @@
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B698" t="s">
         <v>32</v>
@@ -18700,7 +18700,7 @@
     </row>
     <row r="699" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B699" t="s">
         <v>10</v>
@@ -18723,7 +18723,7 @@
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B700" t="s">
         <v>11</v>
@@ -18746,7 +18746,7 @@
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B701" t="s">
         <v>12</v>
@@ -18769,7 +18769,7 @@
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B702" t="s">
         <v>13</v>
@@ -18792,7 +18792,7 @@
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B703" t="s">
         <v>28</v>
@@ -18815,7 +18815,7 @@
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B704" t="s">
         <v>29</v>
@@ -18838,7 +18838,7 @@
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B705" t="s">
         <v>14</v>
@@ -18861,7 +18861,7 @@
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B706" t="s">
         <v>15</v>
@@ -18884,10 +18884,10 @@
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B707" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C707">
         <v>2023</v>
@@ -18907,7 +18907,7 @@
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B708" t="s">
         <v>16</v>
@@ -18930,7 +18930,7 @@
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B709" t="s">
         <v>17</v>
@@ -18953,10 +18953,10 @@
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B710" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C710">
         <v>2023</v>
@@ -18976,7 +18976,7 @@
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B711" t="s">
         <v>18</v>
@@ -18999,7 +18999,7 @@
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B712" t="s">
         <v>19</v>
@@ -19022,7 +19022,7 @@
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B713" t="s">
         <v>20</v>
@@ -19045,7 +19045,7 @@
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B714" t="s">
         <v>21</v>
@@ -19068,7 +19068,7 @@
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B715" t="s">
         <v>37</v>
@@ -19091,10 +19091,10 @@
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B716" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C716">
         <v>2023</v>
@@ -19114,7 +19114,7 @@
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B717" t="s">
         <v>22</v>
@@ -19137,7 +19137,7 @@
     </row>
     <row r="718" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B718" t="s">
         <v>23</v>
@@ -19160,10 +19160,10 @@
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B719" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C719">
         <v>2023</v>
@@ -19183,10 +19183,10 @@
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B720" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C720">
         <v>2023</v>
@@ -19206,10 +19206,10 @@
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B721" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C721">
         <v>2023</v>
@@ -19229,10 +19229,10 @@
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B722" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C722">
         <v>2023</v>
@@ -19252,7 +19252,7 @@
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B723" t="s">
         <v>33</v>
@@ -19275,10 +19275,10 @@
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B724" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C724">
         <v>2023</v>
@@ -19298,10 +19298,10 @@
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B725" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C725">
         <v>2023</v>
@@ -19321,10 +19321,10 @@
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B726" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C726">
         <v>2023</v>
@@ -19344,7 +19344,7 @@
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B727" t="s">
         <v>34</v>
@@ -19367,10 +19367,10 @@
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B728" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C728">
         <v>2023</v>
@@ -19390,7 +19390,7 @@
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B729" t="s">
         <v>2</v>
@@ -19413,7 +19413,7 @@
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B730" t="s">
         <v>3</v>
@@ -19436,7 +19436,7 @@
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B731" t="s">
         <v>35</v>
@@ -19459,7 +19459,7 @@
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B732" t="s">
         <v>4</v>
@@ -19482,7 +19482,7 @@
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B733" t="s">
         <v>5</v>
@@ -19505,7 +19505,7 @@
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B734" t="s">
         <v>6</v>
@@ -19528,7 +19528,7 @@
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B735" t="s">
         <v>40</v>
@@ -19551,7 +19551,7 @@
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B736" t="s">
         <v>7</v>
@@ -19574,7 +19574,7 @@
     </row>
     <row r="737" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B737" t="s">
         <v>36</v>
@@ -19597,7 +19597,7 @@
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B738" t="s">
         <v>8</v>
@@ -19620,7 +19620,7 @@
     </row>
     <row r="739" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B739" t="s">
         <v>9</v>
@@ -19643,7 +19643,7 @@
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B740" t="s">
         <v>31</v>
@@ -19666,7 +19666,7 @@
     </row>
     <row r="741" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B741" t="s">
         <v>32</v>
@@ -19689,7 +19689,7 @@
     </row>
     <row r="742" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B742" t="s">
         <v>10</v>
@@ -19712,7 +19712,7 @@
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B743" t="s">
         <v>11</v>
@@ -19735,7 +19735,7 @@
     </row>
     <row r="744" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B744" t="s">
         <v>12</v>
@@ -19758,7 +19758,7 @@
     </row>
     <row r="745" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B745" t="s">
         <v>13</v>
@@ -19781,7 +19781,7 @@
     </row>
     <row r="746" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B746" t="s">
         <v>28</v>
@@ -19804,7 +19804,7 @@
     </row>
     <row r="747" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B747" t="s">
         <v>29</v>
@@ -19827,7 +19827,7 @@
     </row>
     <row r="748" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B748" t="s">
         <v>14</v>
@@ -19850,7 +19850,7 @@
     </row>
     <row r="749" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B749" t="s">
         <v>15</v>
@@ -19873,10 +19873,10 @@
     </row>
     <row r="750" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B750" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C750">
         <v>2024</v>
@@ -19896,7 +19896,7 @@
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B751" t="s">
         <v>16</v>
@@ -19919,7 +19919,7 @@
     </row>
     <row r="752" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B752" t="s">
         <v>17</v>
@@ -19942,10 +19942,10 @@
     </row>
     <row r="753" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B753" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C753">
         <v>2024</v>
@@ -19965,7 +19965,7 @@
     </row>
     <row r="754" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B754" t="s">
         <v>18</v>
@@ -19988,7 +19988,7 @@
     </row>
     <row r="755" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B755" t="s">
         <v>19</v>
@@ -20011,7 +20011,7 @@
     </row>
     <row r="756" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B756" t="s">
         <v>20</v>
@@ -20034,7 +20034,7 @@
     </row>
     <row r="757" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B757" t="s">
         <v>21</v>
@@ -20057,7 +20057,7 @@
     </row>
     <row r="758" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B758" t="s">
         <v>37</v>
@@ -20080,10 +20080,10 @@
     </row>
     <row r="759" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B759" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C759">
         <v>2024</v>
@@ -20103,7 +20103,7 @@
     </row>
     <row r="760" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B760" t="s">
         <v>22</v>
@@ -20126,7 +20126,7 @@
     </row>
     <row r="761" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B761" t="s">
         <v>23</v>
@@ -20149,10 +20149,10 @@
     </row>
     <row r="762" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B762" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C762">
         <v>2024</v>
@@ -20172,10 +20172,10 @@
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B763" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C763">
         <v>2024</v>
@@ -20195,10 +20195,10 @@
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B764" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C764">
         <v>2024</v>
@@ -20218,10 +20218,10 @@
     </row>
     <row r="765" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B765" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C765">
         <v>2024</v>
@@ -20241,10 +20241,10 @@
     </row>
     <row r="766" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B766" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C766">
         <v>2024</v>
@@ -20264,10 +20264,10 @@
     </row>
     <row r="767" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B767" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C767">
         <v>2024</v>
@@ -20287,10 +20287,10 @@
     </row>
     <row r="768" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B768" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C768">
         <v>2024</v>
@@ -20310,10 +20310,10 @@
     </row>
     <row r="769" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B769" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C769">
         <v>2024</v>
@@ -20333,10 +20333,10 @@
     </row>
     <row r="770" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B770" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C770">
         <v>2024</v>
@@ -20356,10 +20356,10 @@
     </row>
     <row r="771" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B771" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C771">
         <v>2024</v>
@@ -20379,7 +20379,7 @@
     </row>
     <row r="772" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B772" t="s">
         <v>38</v>
@@ -20402,7 +20402,7 @@
     </row>
     <row r="773" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B773" t="s">
         <v>39</v>
@@ -20425,7 +20425,7 @@
     </row>
     <row r="774" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B774" t="s">
         <v>25</v>
@@ -20448,7 +20448,7 @@
     </row>
     <row r="775" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B775" t="s">
         <v>30</v>
@@ -20471,7 +20471,7 @@
     </row>
     <row r="776" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B776" t="s">
         <v>26</v>
@@ -20494,7 +20494,7 @@
     </row>
     <row r="777" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B777" t="s">
         <v>27</v>
@@ -20517,7 +20517,7 @@
     </row>
     <row r="778" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B778" t="s">
         <v>2</v>
@@ -20540,7 +20540,7 @@
     </row>
     <row r="779" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B779" t="s">
         <v>3</v>
@@ -20563,7 +20563,7 @@
     </row>
     <row r="780" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B780" t="s">
         <v>35</v>
@@ -20586,7 +20586,7 @@
     </row>
     <row r="781" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B781" t="s">
         <v>4</v>
@@ -20609,7 +20609,7 @@
     </row>
     <row r="782" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B782" t="s">
         <v>5</v>
@@ -20632,7 +20632,7 @@
     </row>
     <row r="783" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B783" t="s">
         <v>6</v>
@@ -20655,7 +20655,7 @@
     </row>
     <row r="784" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B784" t="s">
         <v>40</v>
@@ -20678,7 +20678,7 @@
     </row>
     <row r="785" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B785" t="s">
         <v>7</v>
@@ -20701,7 +20701,7 @@
     </row>
     <row r="786" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B786" t="s">
         <v>8</v>
@@ -20724,7 +20724,7 @@
     </row>
     <row r="787" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B787" t="s">
         <v>9</v>
@@ -20747,7 +20747,7 @@
     </row>
     <row r="788" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B788" t="s">
         <v>31</v>
@@ -20770,7 +20770,7 @@
     </row>
     <row r="789" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B789" t="s">
         <v>32</v>
@@ -20793,7 +20793,7 @@
     </row>
     <row r="790" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B790" t="s">
         <v>10</v>
@@ -20816,7 +20816,7 @@
     </row>
     <row r="791" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B791" t="s">
         <v>11</v>
@@ -20839,7 +20839,7 @@
     </row>
     <row r="792" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B792" t="s">
         <v>12</v>
@@ -20862,7 +20862,7 @@
     </row>
     <row r="793" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B793" t="s">
         <v>13</v>
@@ -20885,7 +20885,7 @@
     </row>
     <row r="794" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B794" t="s">
         <v>29</v>
@@ -20908,7 +20908,7 @@
     </row>
     <row r="795" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B795" t="s">
         <v>28</v>
@@ -20931,7 +20931,7 @@
     </row>
     <row r="796" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B796" t="s">
         <v>14</v>
@@ -20954,7 +20954,7 @@
     </row>
     <row r="797" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B797" t="s">
         <v>15</v>
@@ -20977,10 +20977,10 @@
     </row>
     <row r="798" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B798" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C798">
         <v>2025</v>
@@ -21000,7 +21000,7 @@
     </row>
     <row r="799" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B799" t="s">
         <v>16</v>
@@ -21023,10 +21023,10 @@
     </row>
     <row r="800" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B800" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C800">
         <v>2025</v>
@@ -21046,7 +21046,7 @@
     </row>
     <row r="801" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B801" t="s">
         <v>17</v>
@@ -21069,7 +21069,7 @@
     </row>
     <row r="802" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B802" t="s">
         <v>18</v>
@@ -21092,7 +21092,7 @@
     </row>
     <row r="803" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B803" t="s">
         <v>19</v>
@@ -21115,7 +21115,7 @@
     </row>
     <row r="804" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B804" t="s">
         <v>20</v>
@@ -21138,7 +21138,7 @@
     </row>
     <row r="805" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B805" t="s">
         <v>21</v>
@@ -21161,7 +21161,7 @@
     </row>
     <row r="806" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B806" t="s">
         <v>22</v>
@@ -21184,7 +21184,7 @@
     </row>
     <row r="807" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B807" t="s">
         <v>23</v>
@@ -21207,7 +21207,7 @@
     </row>
     <row r="808" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B808" t="s">
         <v>36</v>
@@ -21230,7 +21230,7 @@
     </row>
     <row r="809" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B809" t="s">
         <v>37</v>
@@ -21253,10 +21253,10 @@
     </row>
     <row r="810" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B810" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C810">
         <v>2025</v>
@@ -21276,10 +21276,10 @@
     </row>
     <row r="811" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B811" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C811">
         <v>2025</v>
@@ -21299,10 +21299,10 @@
     </row>
     <row r="812" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B812" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C812">
         <v>2025</v>
@@ -21322,10 +21322,10 @@
     </row>
     <row r="813" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B813" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C813">
         <v>2025</v>
@@ -21345,10 +21345,10 @@
     </row>
     <row r="814" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B814" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C814">
         <v>2025</v>
@@ -21368,10 +21368,10 @@
     </row>
     <row r="815" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B815" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C815">
         <v>2025</v>
@@ -21391,10 +21391,10 @@
     </row>
     <row r="816" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B816" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C816">
         <v>2025</v>
@@ -21414,10 +21414,10 @@
     </row>
     <row r="817" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B817" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C817">
         <v>2025</v>
@@ -21437,10 +21437,10 @@
     </row>
     <row r="818" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B818" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C818">
         <v>2025</v>
@@ -21460,10 +21460,10 @@
     </row>
     <row r="819" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B819" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C819">
         <v>2025</v>
@@ -21483,10 +21483,10 @@
     </row>
     <row r="820" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B820" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C820">
         <v>2025</v>
@@ -21506,7 +21506,7 @@
     </row>
     <row r="821" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B821" t="s">
         <v>38</v>
@@ -21529,7 +21529,7 @@
     </row>
     <row r="822" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B822" t="s">
         <v>39</v>
@@ -21552,7 +21552,7 @@
     </row>
     <row r="823" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B823" t="s">
         <v>25</v>
@@ -21575,7 +21575,7 @@
     </row>
     <row r="824" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B824" t="s">
         <v>30</v>
@@ -21598,7 +21598,7 @@
     </row>
     <row r="825" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B825" t="s">
         <v>26</v>
@@ -21621,7 +21621,7 @@
     </row>
     <row r="826" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B826" t="s">
         <v>27</v>
@@ -21644,7 +21644,7 @@
     </row>
     <row r="827" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B827" t="s">
         <v>49</v>
@@ -21667,7 +21667,7 @@
     </row>
     <row r="828" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B828" t="s">
         <v>50</v>
@@ -21690,7 +21690,7 @@
     </row>
     <row r="829" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B829" t="s">
         <v>51</v>
@@ -21713,7 +21713,7 @@
     </row>
     <row r="830" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B830" t="s">
         <v>52</v>
@@ -21736,7 +21736,7 @@
     </row>
     <row r="831" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B831" t="s">
         <v>53</v>
@@ -21759,7 +21759,7 @@
     </row>
     <row r="832" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B832" t="s">
         <v>54</v>
@@ -21782,7 +21782,7 @@
     </row>
     <row r="833" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B833" t="s">
         <v>55</v>
@@ -21805,7 +21805,7 @@
     </row>
     <row r="834" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B834" t="s">
         <v>49</v>
@@ -21828,7 +21828,7 @@
     </row>
     <row r="835" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B835" t="s">
         <v>50</v>
@@ -21851,7 +21851,7 @@
     </row>
     <row r="836" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B836" t="s">
         <v>51</v>
@@ -21874,7 +21874,7 @@
     </row>
     <row r="837" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B837" t="s">
         <v>52</v>
@@ -21897,7 +21897,7 @@
     </row>
     <row r="838" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B838" t="s">
         <v>53</v>
@@ -21920,7 +21920,7 @@
     </row>
     <row r="839" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B839" t="s">
         <v>54</v>
@@ -21943,7 +21943,7 @@
     </row>
     <row r="840" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B840" t="s">
         <v>55</v>
@@ -21966,7 +21966,7 @@
     </row>
     <row r="841" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B841" t="s">
         <v>49</v>
@@ -21989,7 +21989,7 @@
     </row>
     <row r="842" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B842" t="s">
         <v>50</v>
@@ -22012,7 +22012,7 @@
     </row>
     <row r="843" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B843" t="s">
         <v>51</v>
@@ -22035,7 +22035,7 @@
     </row>
     <row r="844" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B844" t="s">
         <v>52</v>
@@ -22058,7 +22058,7 @@
     </row>
     <row r="845" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B845" t="s">
         <v>53</v>
@@ -22081,7 +22081,7 @@
     </row>
     <row r="846" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B846" t="s">
         <v>54</v>
@@ -22104,7 +22104,7 @@
     </row>
     <row r="847" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B847" t="s">
         <v>55</v>
@@ -22127,7 +22127,7 @@
     </row>
     <row r="848" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B848" t="s">
         <v>49</v>
@@ -22150,7 +22150,7 @@
     </row>
     <row r="849" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B849" t="s">
         <v>50</v>
@@ -22173,7 +22173,7 @@
     </row>
     <row r="850" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B850" t="s">
         <v>51</v>
@@ -22196,7 +22196,7 @@
     </row>
     <row r="851" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B851" t="s">
         <v>52</v>
@@ -22219,7 +22219,7 @@
     </row>
     <row r="852" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B852" t="s">
         <v>53</v>
@@ -22242,7 +22242,7 @@
     </row>
     <row r="853" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A853" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B853" t="s">
         <v>54</v>
@@ -22265,7 +22265,7 @@
     </row>
     <row r="854" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B854" t="s">
         <v>55</v>
@@ -22288,7 +22288,7 @@
     </row>
     <row r="855" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B855" t="s">
         <v>49</v>
@@ -22311,7 +22311,7 @@
     </row>
     <row r="856" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B856" t="s">
         <v>50</v>
@@ -22334,7 +22334,7 @@
     </row>
     <row r="857" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B857" t="s">
         <v>51</v>
@@ -22357,7 +22357,7 @@
     </row>
     <row r="858" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A858" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B858" t="s">
         <v>52</v>
@@ -22380,7 +22380,7 @@
     </row>
     <row r="859" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B859" t="s">
         <v>53</v>
@@ -22403,7 +22403,7 @@
     </row>
     <row r="860" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B860" t="s">
         <v>54</v>
@@ -22426,7 +22426,7 @@
     </row>
     <row r="861" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B861" t="s">
         <v>55</v>
@@ -22449,7 +22449,7 @@
     </row>
     <row r="862" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B862" t="s">
         <v>49</v>
@@ -22472,7 +22472,7 @@
     </row>
     <row r="863" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B863" t="s">
         <v>50</v>
@@ -22495,7 +22495,7 @@
     </row>
     <row r="864" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A864" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B864" t="s">
         <v>51</v>
@@ -22516,9 +22516,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="865" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A865" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B865" t="s">
         <v>52</v>
@@ -22539,9 +22539,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="866" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B866" t="s">
         <v>53</v>
@@ -22562,9 +22562,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="867" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B867" t="s">
         <v>54</v>
@@ -22585,9 +22585,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="868" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B868" t="s">
         <v>55</v>
@@ -22606,6 +22606,4521 @@
       </c>
       <c r="G868">
         <v>9</v>
+      </c>
+    </row>
+    <row r="869" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A869" t="s">
+        <v>41</v>
+      </c>
+      <c r="B869" t="s">
+        <v>2</v>
+      </c>
+      <c r="C869">
+        <v>2026</v>
+      </c>
+      <c r="D869">
+        <v>2026</v>
+      </c>
+      <c r="E869">
+        <v>18</v>
+      </c>
+      <c r="F869">
+        <v>18</v>
+      </c>
+      <c r="G869">
+        <v>36</v>
+      </c>
+      <c r="H869">
+        <v>120</v>
+      </c>
+      <c r="I869" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="870" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A870" t="s">
+        <v>41</v>
+      </c>
+      <c r="B870" t="s">
+        <v>3</v>
+      </c>
+      <c r="C870">
+        <v>2026</v>
+      </c>
+      <c r="D870">
+        <v>2026</v>
+      </c>
+      <c r="E870">
+        <v>6</v>
+      </c>
+      <c r="F870">
+        <v>30</v>
+      </c>
+      <c r="G870">
+        <v>36</v>
+      </c>
+      <c r="H870">
+        <v>120</v>
+      </c>
+      <c r="I870" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="871" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A871" t="s">
+        <v>41</v>
+      </c>
+      <c r="B871" t="s">
+        <v>35</v>
+      </c>
+      <c r="C871">
+        <v>2026</v>
+      </c>
+      <c r="D871">
+        <v>2026</v>
+      </c>
+      <c r="E871">
+        <v>6</v>
+      </c>
+      <c r="F871">
+        <v>30</v>
+      </c>
+      <c r="G871">
+        <v>36</v>
+      </c>
+      <c r="H871">
+        <v>120</v>
+      </c>
+      <c r="I871" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="872" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A872" t="s">
+        <v>41</v>
+      </c>
+      <c r="B872" t="s">
+        <v>4</v>
+      </c>
+      <c r="C872">
+        <v>2026</v>
+      </c>
+      <c r="D872">
+        <v>2026</v>
+      </c>
+      <c r="E872">
+        <v>15</v>
+      </c>
+      <c r="F872">
+        <v>24</v>
+      </c>
+      <c r="G872">
+        <v>39</v>
+      </c>
+      <c r="H872">
+        <v>120</v>
+      </c>
+      <c r="I872" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="873" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A873" t="s">
+        <v>41</v>
+      </c>
+      <c r="B873" t="s">
+        <v>5</v>
+      </c>
+      <c r="C873">
+        <v>2026</v>
+      </c>
+      <c r="D873">
+        <v>2026</v>
+      </c>
+      <c r="E873">
+        <v>6</v>
+      </c>
+      <c r="F873">
+        <v>30</v>
+      </c>
+      <c r="G873">
+        <v>36</v>
+      </c>
+      <c r="H873">
+        <v>120</v>
+      </c>
+      <c r="I873" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="874" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A874" t="s">
+        <v>41</v>
+      </c>
+      <c r="B874" t="s">
+        <v>6</v>
+      </c>
+      <c r="C874">
+        <v>2026</v>
+      </c>
+      <c r="D874">
+        <v>2026</v>
+      </c>
+      <c r="E874">
+        <v>18</v>
+      </c>
+      <c r="F874">
+        <v>21</v>
+      </c>
+      <c r="G874">
+        <v>39</v>
+      </c>
+      <c r="H874">
+        <v>130</v>
+      </c>
+      <c r="I874" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="875" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A875" t="s">
+        <v>41</v>
+      </c>
+      <c r="B875" t="s">
+        <v>40</v>
+      </c>
+      <c r="C875">
+        <v>2026</v>
+      </c>
+      <c r="D875">
+        <v>2026</v>
+      </c>
+      <c r="E875">
+        <v>15</v>
+      </c>
+      <c r="F875">
+        <v>24</v>
+      </c>
+      <c r="G875">
+        <v>39</v>
+      </c>
+      <c r="H875">
+        <v>130</v>
+      </c>
+      <c r="I875" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="876" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A876" t="s">
+        <v>41</v>
+      </c>
+      <c r="B876" t="s">
+        <v>7</v>
+      </c>
+      <c r="C876">
+        <v>2026</v>
+      </c>
+      <c r="D876">
+        <v>2026</v>
+      </c>
+      <c r="E876">
+        <v>15</v>
+      </c>
+      <c r="F876">
+        <v>24</v>
+      </c>
+      <c r="G876">
+        <v>39</v>
+      </c>
+      <c r="H876">
+        <v>130</v>
+      </c>
+      <c r="I876" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="877" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A877" t="s">
+        <v>41</v>
+      </c>
+      <c r="B877" t="s">
+        <v>8</v>
+      </c>
+      <c r="C877">
+        <v>2026</v>
+      </c>
+      <c r="D877">
+        <v>2026</v>
+      </c>
+      <c r="E877">
+        <v>18</v>
+      </c>
+      <c r="F877">
+        <v>21</v>
+      </c>
+      <c r="G877">
+        <v>39</v>
+      </c>
+      <c r="H877">
+        <v>130</v>
+      </c>
+      <c r="I877" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="878" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A878" t="s">
+        <v>41</v>
+      </c>
+      <c r="B878" t="s">
+        <v>9</v>
+      </c>
+      <c r="C878">
+        <v>2026</v>
+      </c>
+      <c r="D878">
+        <v>2026</v>
+      </c>
+      <c r="E878">
+        <v>18</v>
+      </c>
+      <c r="F878">
+        <v>21</v>
+      </c>
+      <c r="G878">
+        <v>39</v>
+      </c>
+      <c r="H878">
+        <v>130</v>
+      </c>
+      <c r="I878" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="879" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A879" t="s">
+        <v>41</v>
+      </c>
+      <c r="B879" t="s">
+        <v>31</v>
+      </c>
+      <c r="C879">
+        <v>2026</v>
+      </c>
+      <c r="D879">
+        <v>2026</v>
+      </c>
+      <c r="E879">
+        <v>18</v>
+      </c>
+      <c r="F879">
+        <v>21</v>
+      </c>
+      <c r="G879">
+        <v>39</v>
+      </c>
+      <c r="H879">
+        <v>130</v>
+      </c>
+      <c r="I879" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="880" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A880" t="s">
+        <v>41</v>
+      </c>
+      <c r="B880" t="s">
+        <v>32</v>
+      </c>
+      <c r="C880">
+        <v>2026</v>
+      </c>
+      <c r="D880">
+        <v>2026</v>
+      </c>
+      <c r="E880">
+        <v>18</v>
+      </c>
+      <c r="F880">
+        <v>21</v>
+      </c>
+      <c r="G880">
+        <v>39</v>
+      </c>
+      <c r="H880">
+        <v>130</v>
+      </c>
+      <c r="I880" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="881" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A881" t="s">
+        <v>41</v>
+      </c>
+      <c r="B881" t="s">
+        <v>10</v>
+      </c>
+      <c r="C881">
+        <v>2026</v>
+      </c>
+      <c r="D881">
+        <v>2026</v>
+      </c>
+      <c r="E881">
+        <v>18</v>
+      </c>
+      <c r="F881">
+        <v>21</v>
+      </c>
+      <c r="G881">
+        <v>39</v>
+      </c>
+      <c r="H881">
+        <v>130</v>
+      </c>
+      <c r="I881" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="882" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A882" t="s">
+        <v>41</v>
+      </c>
+      <c r="B882" t="s">
+        <v>11</v>
+      </c>
+      <c r="C882">
+        <v>2026</v>
+      </c>
+      <c r="D882">
+        <v>2026</v>
+      </c>
+      <c r="E882">
+        <v>18</v>
+      </c>
+      <c r="F882">
+        <v>21</v>
+      </c>
+      <c r="G882">
+        <v>39</v>
+      </c>
+      <c r="H882">
+        <v>130</v>
+      </c>
+      <c r="I882" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="883" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A883" t="s">
+        <v>41</v>
+      </c>
+      <c r="B883" t="s">
+        <v>12</v>
+      </c>
+      <c r="C883">
+        <v>2026</v>
+      </c>
+      <c r="D883">
+        <v>2026</v>
+      </c>
+      <c r="E883">
+        <v>15</v>
+      </c>
+      <c r="F883">
+        <v>24</v>
+      </c>
+      <c r="G883">
+        <v>39</v>
+      </c>
+      <c r="H883">
+        <v>130</v>
+      </c>
+      <c r="I883" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="884" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A884" t="s">
+        <v>41</v>
+      </c>
+      <c r="B884" t="s">
+        <v>13</v>
+      </c>
+      <c r="C884">
+        <v>2026</v>
+      </c>
+      <c r="D884">
+        <v>2026</v>
+      </c>
+      <c r="E884">
+        <v>18</v>
+      </c>
+      <c r="F884">
+        <v>21</v>
+      </c>
+      <c r="G884">
+        <v>39</v>
+      </c>
+      <c r="H884">
+        <v>130</v>
+      </c>
+      <c r="I884" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="885" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A885" t="s">
+        <v>41</v>
+      </c>
+      <c r="B885" t="s">
+        <v>29</v>
+      </c>
+      <c r="C885">
+        <v>2026</v>
+      </c>
+      <c r="D885">
+        <v>2026</v>
+      </c>
+      <c r="E885">
+        <v>18</v>
+      </c>
+      <c r="F885">
+        <v>21</v>
+      </c>
+      <c r="G885">
+        <v>39</v>
+      </c>
+      <c r="H885">
+        <v>130</v>
+      </c>
+      <c r="I885" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="886" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A886" t="s">
+        <v>41</v>
+      </c>
+      <c r="B886" t="s">
+        <v>28</v>
+      </c>
+      <c r="C886">
+        <v>2026</v>
+      </c>
+      <c r="D886">
+        <v>2026</v>
+      </c>
+      <c r="E886">
+        <v>18</v>
+      </c>
+      <c r="F886">
+        <v>21</v>
+      </c>
+      <c r="G886">
+        <v>39</v>
+      </c>
+      <c r="H886">
+        <v>130</v>
+      </c>
+      <c r="I886" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="887" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A887" t="s">
+        <v>41</v>
+      </c>
+      <c r="B887" t="s">
+        <v>14</v>
+      </c>
+      <c r="C887">
+        <v>2026</v>
+      </c>
+      <c r="D887">
+        <v>2026</v>
+      </c>
+      <c r="E887">
+        <v>15</v>
+      </c>
+      <c r="F887">
+        <v>24</v>
+      </c>
+      <c r="G887">
+        <v>39</v>
+      </c>
+      <c r="H887">
+        <v>130</v>
+      </c>
+      <c r="I887" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="888" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A888" t="s">
+        <v>41</v>
+      </c>
+      <c r="B888" t="s">
+        <v>15</v>
+      </c>
+      <c r="C888">
+        <v>2026</v>
+      </c>
+      <c r="D888">
+        <v>2026</v>
+      </c>
+      <c r="E888">
+        <v>18</v>
+      </c>
+      <c r="F888">
+        <v>21</v>
+      </c>
+      <c r="G888">
+        <v>39</v>
+      </c>
+      <c r="H888">
+        <v>130</v>
+      </c>
+      <c r="I888" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="889" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A889" t="s">
+        <v>41</v>
+      </c>
+      <c r="B889" t="s">
+        <v>80</v>
+      </c>
+      <c r="C889">
+        <v>2026</v>
+      </c>
+      <c r="D889">
+        <v>2026</v>
+      </c>
+      <c r="E889">
+        <v>15</v>
+      </c>
+      <c r="F889">
+        <v>24</v>
+      </c>
+      <c r="G889">
+        <v>39</v>
+      </c>
+      <c r="H889">
+        <v>130</v>
+      </c>
+      <c r="I889" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="890" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A890" t="s">
+        <v>41</v>
+      </c>
+      <c r="B890" t="s">
+        <v>16</v>
+      </c>
+      <c r="C890">
+        <v>2026</v>
+      </c>
+      <c r="D890">
+        <v>2026</v>
+      </c>
+      <c r="E890">
+        <v>18</v>
+      </c>
+      <c r="F890">
+        <v>21</v>
+      </c>
+      <c r="G890">
+        <v>39</v>
+      </c>
+      <c r="H890">
+        <v>130</v>
+      </c>
+      <c r="I890" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="891" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A891" t="s">
+        <v>41</v>
+      </c>
+      <c r="B891" t="s">
+        <v>81</v>
+      </c>
+      <c r="C891">
+        <v>2026</v>
+      </c>
+      <c r="D891">
+        <v>2026</v>
+      </c>
+      <c r="E891">
+        <v>18</v>
+      </c>
+      <c r="F891">
+        <v>21</v>
+      </c>
+      <c r="G891">
+        <v>39</v>
+      </c>
+      <c r="H891">
+        <v>130</v>
+      </c>
+      <c r="I891" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="892" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A892" t="s">
+        <v>41</v>
+      </c>
+      <c r="B892" t="s">
+        <v>17</v>
+      </c>
+      <c r="C892">
+        <v>2026</v>
+      </c>
+      <c r="D892">
+        <v>2026</v>
+      </c>
+      <c r="E892">
+        <v>18</v>
+      </c>
+      <c r="F892">
+        <v>21</v>
+      </c>
+      <c r="G892">
+        <v>39</v>
+      </c>
+      <c r="H892">
+        <v>130</v>
+      </c>
+      <c r="I892" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="893" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A893" t="s">
+        <v>41</v>
+      </c>
+      <c r="B893" t="s">
+        <v>18</v>
+      </c>
+      <c r="C893">
+        <v>2026</v>
+      </c>
+      <c r="D893">
+        <v>2026</v>
+      </c>
+      <c r="E893">
+        <v>18</v>
+      </c>
+      <c r="F893">
+        <v>21</v>
+      </c>
+      <c r="G893">
+        <v>39</v>
+      </c>
+      <c r="H893">
+        <v>130</v>
+      </c>
+      <c r="I893" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="894" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A894" t="s">
+        <v>41</v>
+      </c>
+      <c r="B894" t="s">
+        <v>19</v>
+      </c>
+      <c r="C894">
+        <v>2026</v>
+      </c>
+      <c r="D894">
+        <v>2026</v>
+      </c>
+      <c r="E894">
+        <v>18</v>
+      </c>
+      <c r="F894">
+        <v>21</v>
+      </c>
+      <c r="G894">
+        <v>39</v>
+      </c>
+      <c r="H894">
+        <v>130</v>
+      </c>
+      <c r="I894" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="895" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A895" t="s">
+        <v>41</v>
+      </c>
+      <c r="B895" t="s">
+        <v>20</v>
+      </c>
+      <c r="C895">
+        <v>2026</v>
+      </c>
+      <c r="D895">
+        <v>2026</v>
+      </c>
+      <c r="E895">
+        <v>18</v>
+      </c>
+      <c r="F895">
+        <v>21</v>
+      </c>
+      <c r="G895">
+        <v>39</v>
+      </c>
+      <c r="H895">
+        <v>130</v>
+      </c>
+      <c r="I895" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="896" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A896" t="s">
+        <v>41</v>
+      </c>
+      <c r="B896" t="s">
+        <v>21</v>
+      </c>
+      <c r="C896">
+        <v>2026</v>
+      </c>
+      <c r="D896">
+        <v>2026</v>
+      </c>
+      <c r="E896">
+        <v>18</v>
+      </c>
+      <c r="F896">
+        <v>21</v>
+      </c>
+      <c r="G896">
+        <v>39</v>
+      </c>
+      <c r="H896">
+        <v>130</v>
+      </c>
+      <c r="I896" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="897" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A897" t="s">
+        <v>41</v>
+      </c>
+      <c r="B897" t="s">
+        <v>22</v>
+      </c>
+      <c r="C897">
+        <v>2026</v>
+      </c>
+      <c r="D897">
+        <v>2026</v>
+      </c>
+      <c r="E897">
+        <v>39</v>
+      </c>
+      <c r="F897">
+        <v>0</v>
+      </c>
+      <c r="G897">
+        <v>39</v>
+      </c>
+      <c r="H897">
+        <v>164</v>
+      </c>
+      <c r="I897" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="898" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A898" t="s">
+        <v>41</v>
+      </c>
+      <c r="B898" t="s">
+        <v>23</v>
+      </c>
+      <c r="C898">
+        <v>2026</v>
+      </c>
+      <c r="D898">
+        <v>2026</v>
+      </c>
+      <c r="E898">
+        <v>18</v>
+      </c>
+      <c r="F898">
+        <v>21</v>
+      </c>
+      <c r="G898">
+        <v>39</v>
+      </c>
+      <c r="H898">
+        <v>130</v>
+      </c>
+      <c r="I898" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="899" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A899" t="s">
+        <v>41</v>
+      </c>
+      <c r="B899" t="s">
+        <v>36</v>
+      </c>
+      <c r="C899">
+        <v>2026</v>
+      </c>
+      <c r="D899">
+        <v>2026</v>
+      </c>
+      <c r="E899">
+        <v>18</v>
+      </c>
+      <c r="F899">
+        <v>21</v>
+      </c>
+      <c r="G899">
+        <v>39</v>
+      </c>
+      <c r="H899">
+        <v>130</v>
+      </c>
+      <c r="I899" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="900" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A900" t="s">
+        <v>41</v>
+      </c>
+      <c r="B900" t="s">
+        <v>37</v>
+      </c>
+      <c r="C900">
+        <v>2026</v>
+      </c>
+      <c r="D900">
+        <v>2026</v>
+      </c>
+      <c r="E900">
+        <v>18</v>
+      </c>
+      <c r="F900">
+        <v>21</v>
+      </c>
+      <c r="G900">
+        <v>39</v>
+      </c>
+      <c r="H900">
+        <v>130</v>
+      </c>
+      <c r="I900" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="901" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A901" t="s">
+        <v>41</v>
+      </c>
+      <c r="B901" t="s">
+        <v>61</v>
+      </c>
+      <c r="C901">
+        <v>2026</v>
+      </c>
+      <c r="D901">
+        <v>2026</v>
+      </c>
+      <c r="E901">
+        <v>14</v>
+      </c>
+      <c r="F901">
+        <v>25</v>
+      </c>
+      <c r="G901">
+        <v>39</v>
+      </c>
+      <c r="H901">
+        <v>130</v>
+      </c>
+      <c r="I901" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="902" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A902" t="s">
+        <v>41</v>
+      </c>
+      <c r="B902" t="s">
+        <v>62</v>
+      </c>
+      <c r="C902">
+        <v>2026</v>
+      </c>
+      <c r="D902">
+        <v>2026</v>
+      </c>
+      <c r="E902">
+        <v>11</v>
+      </c>
+      <c r="F902">
+        <v>28</v>
+      </c>
+      <c r="G902">
+        <v>39</v>
+      </c>
+      <c r="H902">
+        <v>130</v>
+      </c>
+      <c r="I902" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="903" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A903" t="s">
+        <v>41</v>
+      </c>
+      <c r="B903" t="s">
+        <v>63</v>
+      </c>
+      <c r="C903">
+        <v>2026</v>
+      </c>
+      <c r="D903">
+        <v>2026</v>
+      </c>
+      <c r="E903">
+        <v>18</v>
+      </c>
+      <c r="F903">
+        <v>21</v>
+      </c>
+      <c r="G903">
+        <v>39</v>
+      </c>
+      <c r="H903">
+        <v>130</v>
+      </c>
+      <c r="I903" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="904" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A904" t="s">
+        <v>41</v>
+      </c>
+      <c r="B904" t="s">
+        <v>64</v>
+      </c>
+      <c r="C904">
+        <v>2026</v>
+      </c>
+      <c r="D904">
+        <v>2026</v>
+      </c>
+      <c r="E904">
+        <v>12</v>
+      </c>
+      <c r="F904">
+        <v>24</v>
+      </c>
+      <c r="G904">
+        <v>36</v>
+      </c>
+      <c r="H904">
+        <v>120</v>
+      </c>
+      <c r="I904" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="905" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A905" t="s">
+        <v>41</v>
+      </c>
+      <c r="B905" t="s">
+        <v>65</v>
+      </c>
+      <c r="C905">
+        <v>2026</v>
+      </c>
+      <c r="D905">
+        <v>2026</v>
+      </c>
+      <c r="E905">
+        <v>12</v>
+      </c>
+      <c r="F905">
+        <v>24</v>
+      </c>
+      <c r="G905">
+        <v>36</v>
+      </c>
+      <c r="H905">
+        <v>120</v>
+      </c>
+      <c r="I905" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="906" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A906" t="s">
+        <v>41</v>
+      </c>
+      <c r="B906" t="s">
+        <v>66</v>
+      </c>
+      <c r="C906">
+        <v>2026</v>
+      </c>
+      <c r="D906">
+        <v>2026</v>
+      </c>
+      <c r="E906">
+        <v>6</v>
+      </c>
+      <c r="F906">
+        <v>30</v>
+      </c>
+      <c r="G906">
+        <v>36</v>
+      </c>
+      <c r="H906">
+        <v>120</v>
+      </c>
+      <c r="I906" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="907" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A907" t="s">
+        <v>41</v>
+      </c>
+      <c r="B907" t="s">
+        <v>67</v>
+      </c>
+      <c r="C907">
+        <v>2026</v>
+      </c>
+      <c r="D907">
+        <v>2026</v>
+      </c>
+      <c r="E907">
+        <v>14</v>
+      </c>
+      <c r="F907">
+        <v>0</v>
+      </c>
+      <c r="G907">
+        <v>39</v>
+      </c>
+      <c r="H907">
+        <v>130</v>
+      </c>
+      <c r="I907" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="908" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A908" t="s">
+        <v>41</v>
+      </c>
+      <c r="B908" t="s">
+        <v>68</v>
+      </c>
+      <c r="C908">
+        <v>2026</v>
+      </c>
+      <c r="D908">
+        <v>2026</v>
+      </c>
+      <c r="E908">
+        <v>15</v>
+      </c>
+      <c r="F908">
+        <v>21</v>
+      </c>
+      <c r="G908">
+        <v>36</v>
+      </c>
+      <c r="H908">
+        <v>120</v>
+      </c>
+      <c r="I908" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="909" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A909" t="s">
+        <v>41</v>
+      </c>
+      <c r="B909" t="s">
+        <v>69</v>
+      </c>
+      <c r="C909">
+        <v>2026</v>
+      </c>
+      <c r="D909">
+        <v>2026</v>
+      </c>
+      <c r="E909">
+        <v>15</v>
+      </c>
+      <c r="F909">
+        <v>21</v>
+      </c>
+      <c r="G909">
+        <v>36</v>
+      </c>
+      <c r="H909">
+        <v>120</v>
+      </c>
+      <c r="I909" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="910" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A910" t="s">
+        <v>41</v>
+      </c>
+      <c r="B910" t="s">
+        <v>70</v>
+      </c>
+      <c r="C910">
+        <v>2026</v>
+      </c>
+      <c r="D910">
+        <v>2026</v>
+      </c>
+      <c r="E910">
+        <v>18</v>
+      </c>
+      <c r="F910">
+        <v>21</v>
+      </c>
+      <c r="G910">
+        <v>39</v>
+      </c>
+      <c r="H910">
+        <v>130</v>
+      </c>
+      <c r="I910" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="911" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A911" t="s">
+        <v>41</v>
+      </c>
+      <c r="B911" t="s">
+        <v>71</v>
+      </c>
+      <c r="C911">
+        <v>2026</v>
+      </c>
+      <c r="D911">
+        <v>2026</v>
+      </c>
+      <c r="E911">
+        <v>15</v>
+      </c>
+      <c r="F911">
+        <v>24</v>
+      </c>
+      <c r="G911">
+        <v>39</v>
+      </c>
+      <c r="H911">
+        <v>130</v>
+      </c>
+      <c r="I911" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="912" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A912" t="s">
+        <v>41</v>
+      </c>
+      <c r="B912" t="s">
+        <v>38</v>
+      </c>
+      <c r="C912">
+        <v>2026</v>
+      </c>
+      <c r="D912">
+        <v>2026</v>
+      </c>
+      <c r="E912">
+        <v>12</v>
+      </c>
+      <c r="F912">
+        <v>27</v>
+      </c>
+      <c r="G912">
+        <v>39</v>
+      </c>
+      <c r="H912">
+        <v>130</v>
+      </c>
+      <c r="I912" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="913" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A913" t="s">
+        <v>41</v>
+      </c>
+      <c r="B913" t="s">
+        <v>39</v>
+      </c>
+      <c r="C913">
+        <v>2026</v>
+      </c>
+      <c r="D913">
+        <v>2026</v>
+      </c>
+      <c r="E913">
+        <v>9</v>
+      </c>
+      <c r="F913">
+        <v>27</v>
+      </c>
+      <c r="G913">
+        <v>36</v>
+      </c>
+      <c r="H913">
+        <v>120</v>
+      </c>
+      <c r="I913" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="914" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A914" t="s">
+        <v>41</v>
+      </c>
+      <c r="B914" t="s">
+        <v>25</v>
+      </c>
+      <c r="C914">
+        <v>2026</v>
+      </c>
+      <c r="D914">
+        <v>2026</v>
+      </c>
+      <c r="E914">
+        <v>9</v>
+      </c>
+      <c r="F914">
+        <v>27</v>
+      </c>
+      <c r="G914">
+        <v>36</v>
+      </c>
+      <c r="H914">
+        <v>120</v>
+      </c>
+      <c r="I914" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="915" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A915" t="s">
+        <v>41</v>
+      </c>
+      <c r="B915" t="s">
+        <v>30</v>
+      </c>
+      <c r="C915">
+        <v>2026</v>
+      </c>
+      <c r="D915">
+        <v>2026</v>
+      </c>
+      <c r="E915">
+        <v>6</v>
+      </c>
+      <c r="F915">
+        <v>30</v>
+      </c>
+      <c r="G915">
+        <v>36</v>
+      </c>
+      <c r="H915">
+        <v>120</v>
+      </c>
+      <c r="I915" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="916" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A916" t="s">
+        <v>41</v>
+      </c>
+      <c r="B916" t="s">
+        <v>26</v>
+      </c>
+      <c r="C916">
+        <v>2026</v>
+      </c>
+      <c r="D916">
+        <v>2026</v>
+      </c>
+      <c r="E916">
+        <v>12</v>
+      </c>
+      <c r="F916">
+        <v>24</v>
+      </c>
+      <c r="G916">
+        <v>36</v>
+      </c>
+      <c r="H916">
+        <v>120</v>
+      </c>
+      <c r="I916" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="917" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A917" t="s">
+        <v>41</v>
+      </c>
+      <c r="B917" t="s">
+        <v>27</v>
+      </c>
+      <c r="C917">
+        <v>2026</v>
+      </c>
+      <c r="D917">
+        <v>2026</v>
+      </c>
+      <c r="E917">
+        <v>13</v>
+      </c>
+      <c r="F917">
+        <v>26</v>
+      </c>
+      <c r="G917">
+        <v>39</v>
+      </c>
+      <c r="H917">
+        <v>130</v>
+      </c>
+      <c r="I917" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="918" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A918" t="s">
+        <v>43</v>
+      </c>
+      <c r="B918" t="s">
+        <v>2</v>
+      </c>
+      <c r="C918">
+        <v>2026</v>
+      </c>
+      <c r="D918">
+        <v>2026</v>
+      </c>
+      <c r="E918">
+        <v>18</v>
+      </c>
+      <c r="F918">
+        <v>9</v>
+      </c>
+      <c r="G918">
+        <v>27</v>
+      </c>
+      <c r="I918" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="919" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A919" t="s">
+        <v>43</v>
+      </c>
+      <c r="B919" t="s">
+        <v>3</v>
+      </c>
+      <c r="C919">
+        <v>2026</v>
+      </c>
+      <c r="D919">
+        <v>2026</v>
+      </c>
+      <c r="E919">
+        <v>6</v>
+      </c>
+      <c r="F919">
+        <v>21</v>
+      </c>
+      <c r="G919">
+        <v>27</v>
+      </c>
+      <c r="I919" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="920" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A920" t="s">
+        <v>43</v>
+      </c>
+      <c r="B920" t="s">
+        <v>35</v>
+      </c>
+      <c r="C920">
+        <v>2026</v>
+      </c>
+      <c r="D920">
+        <v>2026</v>
+      </c>
+      <c r="E920">
+        <v>6</v>
+      </c>
+      <c r="F920">
+        <v>21</v>
+      </c>
+      <c r="G920">
+        <v>27</v>
+      </c>
+      <c r="I920" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="921" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A921" t="s">
+        <v>43</v>
+      </c>
+      <c r="B921" t="s">
+        <v>4</v>
+      </c>
+      <c r="C921">
+        <v>2026</v>
+      </c>
+      <c r="D921">
+        <v>2026</v>
+      </c>
+      <c r="E921">
+        <v>15</v>
+      </c>
+      <c r="F921">
+        <v>12</v>
+      </c>
+      <c r="G921">
+        <v>27</v>
+      </c>
+      <c r="I921" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="922" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A922" t="s">
+        <v>43</v>
+      </c>
+      <c r="B922" t="s">
+        <v>5</v>
+      </c>
+      <c r="C922">
+        <v>2026</v>
+      </c>
+      <c r="D922">
+        <v>2026</v>
+      </c>
+      <c r="E922">
+        <v>6</v>
+      </c>
+      <c r="F922">
+        <v>21</v>
+      </c>
+      <c r="G922">
+        <v>27</v>
+      </c>
+      <c r="I922" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="923" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A923" t="s">
+        <v>43</v>
+      </c>
+      <c r="B923" t="s">
+        <v>6</v>
+      </c>
+      <c r="C923">
+        <v>2026</v>
+      </c>
+      <c r="D923">
+        <v>2026</v>
+      </c>
+      <c r="E923">
+        <v>18</v>
+      </c>
+      <c r="F923">
+        <v>9</v>
+      </c>
+      <c r="G923">
+        <v>27</v>
+      </c>
+      <c r="I923" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="924" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A924" t="s">
+        <v>43</v>
+      </c>
+      <c r="B924" t="s">
+        <v>40</v>
+      </c>
+      <c r="C924">
+        <v>2026</v>
+      </c>
+      <c r="D924">
+        <v>2026</v>
+      </c>
+      <c r="E924">
+        <v>15</v>
+      </c>
+      <c r="F924">
+        <v>12</v>
+      </c>
+      <c r="G924">
+        <v>27</v>
+      </c>
+      <c r="I924" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="925" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A925" t="s">
+        <v>43</v>
+      </c>
+      <c r="B925" t="s">
+        <v>7</v>
+      </c>
+      <c r="C925">
+        <v>2026</v>
+      </c>
+      <c r="D925">
+        <v>2026</v>
+      </c>
+      <c r="E925">
+        <v>15</v>
+      </c>
+      <c r="F925">
+        <v>12</v>
+      </c>
+      <c r="G925">
+        <v>27</v>
+      </c>
+      <c r="I925" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="926" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A926" t="s">
+        <v>43</v>
+      </c>
+      <c r="B926" t="s">
+        <v>8</v>
+      </c>
+      <c r="C926">
+        <v>2026</v>
+      </c>
+      <c r="D926">
+        <v>2026</v>
+      </c>
+      <c r="E926">
+        <v>18</v>
+      </c>
+      <c r="F926">
+        <v>9</v>
+      </c>
+      <c r="G926">
+        <v>27</v>
+      </c>
+      <c r="I926" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="927" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A927" t="s">
+        <v>43</v>
+      </c>
+      <c r="B927" t="s">
+        <v>9</v>
+      </c>
+      <c r="C927">
+        <v>2026</v>
+      </c>
+      <c r="D927">
+        <v>2026</v>
+      </c>
+      <c r="E927">
+        <v>18</v>
+      </c>
+      <c r="F927">
+        <v>9</v>
+      </c>
+      <c r="G927">
+        <v>27</v>
+      </c>
+      <c r="I927" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="928" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A928" t="s">
+        <v>43</v>
+      </c>
+      <c r="B928" t="s">
+        <v>31</v>
+      </c>
+      <c r="C928">
+        <v>2026</v>
+      </c>
+      <c r="D928">
+        <v>2026</v>
+      </c>
+      <c r="E928">
+        <v>18</v>
+      </c>
+      <c r="F928">
+        <v>9</v>
+      </c>
+      <c r="G928">
+        <v>27</v>
+      </c>
+      <c r="I928" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="929" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A929" t="s">
+        <v>43</v>
+      </c>
+      <c r="B929" t="s">
+        <v>32</v>
+      </c>
+      <c r="C929">
+        <v>2026</v>
+      </c>
+      <c r="D929">
+        <v>2026</v>
+      </c>
+      <c r="E929">
+        <v>18</v>
+      </c>
+      <c r="F929">
+        <v>9</v>
+      </c>
+      <c r="G929">
+        <v>27</v>
+      </c>
+      <c r="I929" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="930" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A930" t="s">
+        <v>43</v>
+      </c>
+      <c r="B930" t="s">
+        <v>10</v>
+      </c>
+      <c r="C930">
+        <v>2026</v>
+      </c>
+      <c r="D930">
+        <v>2026</v>
+      </c>
+      <c r="E930">
+        <v>18</v>
+      </c>
+      <c r="F930">
+        <v>9</v>
+      </c>
+      <c r="G930">
+        <v>27</v>
+      </c>
+      <c r="I930" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="931" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A931" t="s">
+        <v>43</v>
+      </c>
+      <c r="B931" t="s">
+        <v>11</v>
+      </c>
+      <c r="C931">
+        <v>2026</v>
+      </c>
+      <c r="D931">
+        <v>2026</v>
+      </c>
+      <c r="E931">
+        <v>18</v>
+      </c>
+      <c r="F931">
+        <v>9</v>
+      </c>
+      <c r="G931">
+        <v>27</v>
+      </c>
+      <c r="I931" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="932" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A932" t="s">
+        <v>43</v>
+      </c>
+      <c r="B932" t="s">
+        <v>12</v>
+      </c>
+      <c r="C932">
+        <v>2026</v>
+      </c>
+      <c r="D932">
+        <v>2026</v>
+      </c>
+      <c r="E932">
+        <v>15</v>
+      </c>
+      <c r="F932">
+        <v>12</v>
+      </c>
+      <c r="G932">
+        <v>27</v>
+      </c>
+      <c r="I932" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="933" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A933" t="s">
+        <v>43</v>
+      </c>
+      <c r="B933" t="s">
+        <v>13</v>
+      </c>
+      <c r="C933">
+        <v>2026</v>
+      </c>
+      <c r="D933">
+        <v>2026</v>
+      </c>
+      <c r="E933">
+        <v>18</v>
+      </c>
+      <c r="F933">
+        <v>9</v>
+      </c>
+      <c r="G933">
+        <v>27</v>
+      </c>
+      <c r="I933" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="934" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A934" t="s">
+        <v>43</v>
+      </c>
+      <c r="B934" t="s">
+        <v>29</v>
+      </c>
+      <c r="C934">
+        <v>2026</v>
+      </c>
+      <c r="D934">
+        <v>2026</v>
+      </c>
+      <c r="E934">
+        <v>18</v>
+      </c>
+      <c r="F934">
+        <v>9</v>
+      </c>
+      <c r="G934">
+        <v>27</v>
+      </c>
+      <c r="I934" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="935" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A935" t="s">
+        <v>43</v>
+      </c>
+      <c r="B935" t="s">
+        <v>28</v>
+      </c>
+      <c r="C935">
+        <v>2026</v>
+      </c>
+      <c r="D935">
+        <v>2026</v>
+      </c>
+      <c r="E935">
+        <v>18</v>
+      </c>
+      <c r="F935">
+        <v>9</v>
+      </c>
+      <c r="G935">
+        <v>27</v>
+      </c>
+      <c r="I935" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="936" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A936" t="s">
+        <v>43</v>
+      </c>
+      <c r="B936" t="s">
+        <v>14</v>
+      </c>
+      <c r="C936">
+        <v>2026</v>
+      </c>
+      <c r="D936">
+        <v>2026</v>
+      </c>
+      <c r="E936">
+        <v>15</v>
+      </c>
+      <c r="F936">
+        <v>12</v>
+      </c>
+      <c r="G936">
+        <v>27</v>
+      </c>
+      <c r="I936" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A937" t="s">
+        <v>43</v>
+      </c>
+      <c r="B937" t="s">
+        <v>15</v>
+      </c>
+      <c r="C937">
+        <v>2026</v>
+      </c>
+      <c r="D937">
+        <v>2026</v>
+      </c>
+      <c r="E937">
+        <v>18</v>
+      </c>
+      <c r="F937">
+        <v>9</v>
+      </c>
+      <c r="G937">
+        <v>27</v>
+      </c>
+      <c r="I937" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="938" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A938" t="s">
+        <v>43</v>
+      </c>
+      <c r="B938" t="s">
+        <v>80</v>
+      </c>
+      <c r="C938">
+        <v>2026</v>
+      </c>
+      <c r="D938">
+        <v>2026</v>
+      </c>
+      <c r="E938">
+        <v>15</v>
+      </c>
+      <c r="F938">
+        <v>12</v>
+      </c>
+      <c r="G938">
+        <v>27</v>
+      </c>
+      <c r="I938" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A939" t="s">
+        <v>43</v>
+      </c>
+      <c r="B939" t="s">
+        <v>16</v>
+      </c>
+      <c r="C939">
+        <v>2026</v>
+      </c>
+      <c r="D939">
+        <v>2026</v>
+      </c>
+      <c r="E939">
+        <v>18</v>
+      </c>
+      <c r="F939">
+        <v>9</v>
+      </c>
+      <c r="G939">
+        <v>27</v>
+      </c>
+      <c r="I939" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A940" t="s">
+        <v>43</v>
+      </c>
+      <c r="B940" t="s">
+        <v>81</v>
+      </c>
+      <c r="C940">
+        <v>2026</v>
+      </c>
+      <c r="D940">
+        <v>2026</v>
+      </c>
+      <c r="E940">
+        <v>18</v>
+      </c>
+      <c r="F940">
+        <v>9</v>
+      </c>
+      <c r="G940">
+        <v>27</v>
+      </c>
+      <c r="I940" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A941" t="s">
+        <v>43</v>
+      </c>
+      <c r="B941" t="s">
+        <v>17</v>
+      </c>
+      <c r="C941">
+        <v>2026</v>
+      </c>
+      <c r="D941">
+        <v>2026</v>
+      </c>
+      <c r="E941">
+        <v>18</v>
+      </c>
+      <c r="F941">
+        <v>9</v>
+      </c>
+      <c r="G941">
+        <v>27</v>
+      </c>
+      <c r="I941" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A942" t="s">
+        <v>43</v>
+      </c>
+      <c r="B942" t="s">
+        <v>18</v>
+      </c>
+      <c r="C942">
+        <v>2026</v>
+      </c>
+      <c r="D942">
+        <v>2026</v>
+      </c>
+      <c r="E942">
+        <v>18</v>
+      </c>
+      <c r="F942">
+        <v>9</v>
+      </c>
+      <c r="G942">
+        <v>27</v>
+      </c>
+      <c r="I942" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="943" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A943" t="s">
+        <v>43</v>
+      </c>
+      <c r="B943" t="s">
+        <v>19</v>
+      </c>
+      <c r="C943">
+        <v>2026</v>
+      </c>
+      <c r="D943">
+        <v>2026</v>
+      </c>
+      <c r="E943">
+        <v>18</v>
+      </c>
+      <c r="F943">
+        <v>9</v>
+      </c>
+      <c r="G943">
+        <v>27</v>
+      </c>
+      <c r="I943" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="944" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A944" t="s">
+        <v>43</v>
+      </c>
+      <c r="B944" t="s">
+        <v>20</v>
+      </c>
+      <c r="C944">
+        <v>2026</v>
+      </c>
+      <c r="D944">
+        <v>2026</v>
+      </c>
+      <c r="E944">
+        <v>18</v>
+      </c>
+      <c r="F944">
+        <v>9</v>
+      </c>
+      <c r="G944">
+        <v>27</v>
+      </c>
+      <c r="I944" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A945" t="s">
+        <v>43</v>
+      </c>
+      <c r="B945" t="s">
+        <v>21</v>
+      </c>
+      <c r="C945">
+        <v>2026</v>
+      </c>
+      <c r="D945">
+        <v>2026</v>
+      </c>
+      <c r="E945">
+        <v>18</v>
+      </c>
+      <c r="F945">
+        <v>9</v>
+      </c>
+      <c r="G945">
+        <v>27</v>
+      </c>
+      <c r="I945" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A946" t="s">
+        <v>43</v>
+      </c>
+      <c r="B946" t="s">
+        <v>22</v>
+      </c>
+      <c r="C946">
+        <v>2026</v>
+      </c>
+      <c r="D946">
+        <v>2026</v>
+      </c>
+      <c r="E946">
+        <v>27</v>
+      </c>
+      <c r="F946">
+        <v>0</v>
+      </c>
+      <c r="G946">
+        <v>27</v>
+      </c>
+      <c r="I946" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A947" t="s">
+        <v>43</v>
+      </c>
+      <c r="B947" t="s">
+        <v>23</v>
+      </c>
+      <c r="C947">
+        <v>2026</v>
+      </c>
+      <c r="D947">
+        <v>2026</v>
+      </c>
+      <c r="E947">
+        <v>18</v>
+      </c>
+      <c r="F947">
+        <v>9</v>
+      </c>
+      <c r="G947">
+        <v>27</v>
+      </c>
+      <c r="I947" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="948" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A948" t="s">
+        <v>43</v>
+      </c>
+      <c r="B948" t="s">
+        <v>36</v>
+      </c>
+      <c r="C948">
+        <v>2026</v>
+      </c>
+      <c r="D948">
+        <v>2026</v>
+      </c>
+      <c r="E948">
+        <v>18</v>
+      </c>
+      <c r="F948">
+        <v>9</v>
+      </c>
+      <c r="G948">
+        <v>27</v>
+      </c>
+      <c r="I948" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="949" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A949" t="s">
+        <v>43</v>
+      </c>
+      <c r="B949" t="s">
+        <v>37</v>
+      </c>
+      <c r="C949">
+        <v>2026</v>
+      </c>
+      <c r="D949">
+        <v>2026</v>
+      </c>
+      <c r="E949">
+        <v>18</v>
+      </c>
+      <c r="F949">
+        <v>9</v>
+      </c>
+      <c r="G949">
+        <v>27</v>
+      </c>
+      <c r="I949" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A950" t="s">
+        <v>43</v>
+      </c>
+      <c r="B950" t="s">
+        <v>61</v>
+      </c>
+      <c r="C950">
+        <v>2026</v>
+      </c>
+      <c r="D950">
+        <v>2026</v>
+      </c>
+      <c r="E950">
+        <v>14</v>
+      </c>
+      <c r="F950">
+        <v>13</v>
+      </c>
+      <c r="G950">
+        <v>27</v>
+      </c>
+      <c r="I950" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="951" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A951" t="s">
+        <v>43</v>
+      </c>
+      <c r="B951" t="s">
+        <v>62</v>
+      </c>
+      <c r="C951">
+        <v>2026</v>
+      </c>
+      <c r="D951">
+        <v>2026</v>
+      </c>
+      <c r="E951">
+        <v>11</v>
+      </c>
+      <c r="F951">
+        <v>16</v>
+      </c>
+      <c r="G951">
+        <v>27</v>
+      </c>
+      <c r="I951" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="952" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A952" t="s">
+        <v>43</v>
+      </c>
+      <c r="B952" t="s">
+        <v>63</v>
+      </c>
+      <c r="C952">
+        <v>2026</v>
+      </c>
+      <c r="D952">
+        <v>2026</v>
+      </c>
+      <c r="E952">
+        <v>18</v>
+      </c>
+      <c r="F952">
+        <v>9</v>
+      </c>
+      <c r="G952">
+        <v>27</v>
+      </c>
+      <c r="I952" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="953" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A953" t="s">
+        <v>43</v>
+      </c>
+      <c r="B953" t="s">
+        <v>64</v>
+      </c>
+      <c r="C953">
+        <v>2026</v>
+      </c>
+      <c r="D953">
+        <v>2026</v>
+      </c>
+      <c r="E953">
+        <v>12</v>
+      </c>
+      <c r="F953">
+        <v>15</v>
+      </c>
+      <c r="G953">
+        <v>27</v>
+      </c>
+      <c r="I953" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="954" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A954" t="s">
+        <v>43</v>
+      </c>
+      <c r="B954" t="s">
+        <v>65</v>
+      </c>
+      <c r="C954">
+        <v>2026</v>
+      </c>
+      <c r="D954">
+        <v>2026</v>
+      </c>
+      <c r="E954">
+        <v>12</v>
+      </c>
+      <c r="F954">
+        <v>15</v>
+      </c>
+      <c r="G954">
+        <v>27</v>
+      </c>
+      <c r="I954" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="955" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A955" t="s">
+        <v>43</v>
+      </c>
+      <c r="B955" t="s">
+        <v>66</v>
+      </c>
+      <c r="C955">
+        <v>2026</v>
+      </c>
+      <c r="D955">
+        <v>2026</v>
+      </c>
+      <c r="E955">
+        <v>6</v>
+      </c>
+      <c r="F955">
+        <v>21</v>
+      </c>
+      <c r="G955">
+        <v>27</v>
+      </c>
+      <c r="I955" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="956" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A956" t="s">
+        <v>43</v>
+      </c>
+      <c r="B956" t="s">
+        <v>67</v>
+      </c>
+      <c r="C956">
+        <v>2026</v>
+      </c>
+      <c r="D956">
+        <v>2026</v>
+      </c>
+      <c r="E956">
+        <v>14</v>
+      </c>
+      <c r="F956">
+        <v>13</v>
+      </c>
+      <c r="G956">
+        <v>27</v>
+      </c>
+      <c r="I956" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="957" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A957" t="s">
+        <v>43</v>
+      </c>
+      <c r="B957" t="s">
+        <v>68</v>
+      </c>
+      <c r="C957">
+        <v>2026</v>
+      </c>
+      <c r="D957">
+        <v>2026</v>
+      </c>
+      <c r="E957">
+        <v>15</v>
+      </c>
+      <c r="F957">
+        <v>12</v>
+      </c>
+      <c r="G957">
+        <v>27</v>
+      </c>
+      <c r="I957" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="958" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A958" t="s">
+        <v>43</v>
+      </c>
+      <c r="B958" t="s">
+        <v>69</v>
+      </c>
+      <c r="C958">
+        <v>2026</v>
+      </c>
+      <c r="D958">
+        <v>2026</v>
+      </c>
+      <c r="E958">
+        <v>15</v>
+      </c>
+      <c r="F958">
+        <v>12</v>
+      </c>
+      <c r="G958">
+        <v>27</v>
+      </c>
+      <c r="I958" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="959" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A959" t="s">
+        <v>43</v>
+      </c>
+      <c r="B959" t="s">
+        <v>70</v>
+      </c>
+      <c r="C959">
+        <v>2026</v>
+      </c>
+      <c r="D959">
+        <v>2026</v>
+      </c>
+      <c r="E959">
+        <v>18</v>
+      </c>
+      <c r="F959">
+        <v>9</v>
+      </c>
+      <c r="G959">
+        <v>27</v>
+      </c>
+      <c r="I959" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="960" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A960" t="s">
+        <v>43</v>
+      </c>
+      <c r="B960" t="s">
+        <v>71</v>
+      </c>
+      <c r="C960">
+        <v>2026</v>
+      </c>
+      <c r="D960">
+        <v>2026</v>
+      </c>
+      <c r="E960">
+        <v>15</v>
+      </c>
+      <c r="F960">
+        <v>12</v>
+      </c>
+      <c r="G960">
+        <v>27</v>
+      </c>
+      <c r="I960" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="961" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A961" t="s">
+        <v>43</v>
+      </c>
+      <c r="B961" t="s">
+        <v>38</v>
+      </c>
+      <c r="C961">
+        <v>2026</v>
+      </c>
+      <c r="D961">
+        <v>2026</v>
+      </c>
+      <c r="E961">
+        <v>12</v>
+      </c>
+      <c r="F961">
+        <v>15</v>
+      </c>
+      <c r="G961">
+        <v>27</v>
+      </c>
+      <c r="I961" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="962" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A962" t="s">
+        <v>43</v>
+      </c>
+      <c r="B962" t="s">
+        <v>39</v>
+      </c>
+      <c r="C962">
+        <v>2026</v>
+      </c>
+      <c r="D962">
+        <v>2026</v>
+      </c>
+      <c r="E962">
+        <v>9</v>
+      </c>
+      <c r="F962">
+        <v>18</v>
+      </c>
+      <c r="G962">
+        <v>27</v>
+      </c>
+      <c r="I962" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="963" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A963" t="s">
+        <v>43</v>
+      </c>
+      <c r="B963" t="s">
+        <v>25</v>
+      </c>
+      <c r="C963">
+        <v>2026</v>
+      </c>
+      <c r="D963">
+        <v>2026</v>
+      </c>
+      <c r="E963">
+        <v>9</v>
+      </c>
+      <c r="F963">
+        <v>18</v>
+      </c>
+      <c r="G963">
+        <v>27</v>
+      </c>
+      <c r="I963" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="964" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A964" t="s">
+        <v>43</v>
+      </c>
+      <c r="B964" t="s">
+        <v>30</v>
+      </c>
+      <c r="C964">
+        <v>2026</v>
+      </c>
+      <c r="D964">
+        <v>2026</v>
+      </c>
+      <c r="E964">
+        <v>6</v>
+      </c>
+      <c r="F964">
+        <v>21</v>
+      </c>
+      <c r="G964">
+        <v>27</v>
+      </c>
+      <c r="I964" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="965" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A965" t="s">
+        <v>43</v>
+      </c>
+      <c r="B965" t="s">
+        <v>26</v>
+      </c>
+      <c r="C965">
+        <v>2026</v>
+      </c>
+      <c r="D965">
+        <v>2026</v>
+      </c>
+      <c r="E965">
+        <v>12</v>
+      </c>
+      <c r="F965">
+        <v>15</v>
+      </c>
+      <c r="G965">
+        <v>27</v>
+      </c>
+      <c r="I965" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="966" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A966" t="s">
+        <v>43</v>
+      </c>
+      <c r="B966" t="s">
+        <v>27</v>
+      </c>
+      <c r="C966">
+        <v>2026</v>
+      </c>
+      <c r="D966">
+        <v>2026</v>
+      </c>
+      <c r="E966">
+        <v>13</v>
+      </c>
+      <c r="F966">
+        <v>14</v>
+      </c>
+      <c r="G966">
+        <v>27</v>
+      </c>
+      <c r="I966" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="967" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A967" t="s">
+        <v>56</v>
+      </c>
+      <c r="B967" t="s">
+        <v>49</v>
+      </c>
+      <c r="C967">
+        <v>2026</v>
+      </c>
+      <c r="D967">
+        <v>2026</v>
+      </c>
+      <c r="E967">
+        <v>18</v>
+      </c>
+      <c r="F967">
+        <v>21</v>
+      </c>
+      <c r="G967">
+        <v>39</v>
+      </c>
+      <c r="I967" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="968" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A968" t="s">
+        <v>56</v>
+      </c>
+      <c r="B968" t="s">
+        <v>50</v>
+      </c>
+      <c r="C968">
+        <v>2026</v>
+      </c>
+      <c r="D968">
+        <v>2026</v>
+      </c>
+      <c r="E968">
+        <v>18</v>
+      </c>
+      <c r="F968">
+        <v>21</v>
+      </c>
+      <c r="G968">
+        <v>39</v>
+      </c>
+      <c r="I968" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="969" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A969" t="s">
+        <v>56</v>
+      </c>
+      <c r="B969" t="s">
+        <v>51</v>
+      </c>
+      <c r="C969">
+        <v>2026</v>
+      </c>
+      <c r="D969">
+        <v>2026</v>
+      </c>
+      <c r="E969">
+        <v>18</v>
+      </c>
+      <c r="F969">
+        <v>21</v>
+      </c>
+      <c r="G969">
+        <v>39</v>
+      </c>
+      <c r="I969" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="970" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A970" t="s">
+        <v>56</v>
+      </c>
+      <c r="B970" t="s">
+        <v>52</v>
+      </c>
+      <c r="C970">
+        <v>2026</v>
+      </c>
+      <c r="D970">
+        <v>2026</v>
+      </c>
+      <c r="E970">
+        <v>18</v>
+      </c>
+      <c r="F970">
+        <v>21</v>
+      </c>
+      <c r="G970">
+        <v>39</v>
+      </c>
+      <c r="I970" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="971" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A971" t="s">
+        <v>56</v>
+      </c>
+      <c r="B971" t="s">
+        <v>53</v>
+      </c>
+      <c r="C971">
+        <v>2026</v>
+      </c>
+      <c r="D971">
+        <v>2026</v>
+      </c>
+      <c r="E971">
+        <v>18</v>
+      </c>
+      <c r="F971">
+        <v>21</v>
+      </c>
+      <c r="G971">
+        <v>39</v>
+      </c>
+      <c r="I971" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="972" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A972" t="s">
+        <v>56</v>
+      </c>
+      <c r="B972" t="s">
+        <v>54</v>
+      </c>
+      <c r="C972">
+        <v>2026</v>
+      </c>
+      <c r="D972">
+        <v>2026</v>
+      </c>
+      <c r="E972">
+        <v>18</v>
+      </c>
+      <c r="F972">
+        <v>21</v>
+      </c>
+      <c r="G972">
+        <v>39</v>
+      </c>
+      <c r="I972" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="973" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A973" t="s">
+        <v>56</v>
+      </c>
+      <c r="B973" t="s">
+        <v>55</v>
+      </c>
+      <c r="C973">
+        <v>2026</v>
+      </c>
+      <c r="D973">
+        <v>2026</v>
+      </c>
+      <c r="E973">
+        <v>12</v>
+      </c>
+      <c r="F973">
+        <v>27</v>
+      </c>
+      <c r="G973">
+        <v>39</v>
+      </c>
+      <c r="I973" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="974" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A974" t="s">
+        <v>57</v>
+      </c>
+      <c r="B974" t="s">
+        <v>49</v>
+      </c>
+      <c r="C974">
+        <v>2026</v>
+      </c>
+      <c r="D974">
+        <v>2026</v>
+      </c>
+      <c r="E974">
+        <v>18</v>
+      </c>
+      <c r="F974">
+        <v>9</v>
+      </c>
+      <c r="G974">
+        <v>27</v>
+      </c>
+      <c r="I974" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="975" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A975" t="s">
+        <v>57</v>
+      </c>
+      <c r="B975" t="s">
+        <v>50</v>
+      </c>
+      <c r="C975">
+        <v>2026</v>
+      </c>
+      <c r="D975">
+        <v>2026</v>
+      </c>
+      <c r="E975">
+        <v>18</v>
+      </c>
+      <c r="F975">
+        <v>9</v>
+      </c>
+      <c r="G975">
+        <v>27</v>
+      </c>
+      <c r="I975" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A976" t="s">
+        <v>57</v>
+      </c>
+      <c r="B976" t="s">
+        <v>51</v>
+      </c>
+      <c r="C976">
+        <v>2026</v>
+      </c>
+      <c r="D976">
+        <v>2026</v>
+      </c>
+      <c r="E976">
+        <v>18</v>
+      </c>
+      <c r="F976">
+        <v>9</v>
+      </c>
+      <c r="G976">
+        <v>27</v>
+      </c>
+      <c r="I976" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="977" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A977" t="s">
+        <v>57</v>
+      </c>
+      <c r="B977" t="s">
+        <v>52</v>
+      </c>
+      <c r="C977">
+        <v>2026</v>
+      </c>
+      <c r="D977">
+        <v>2026</v>
+      </c>
+      <c r="E977">
+        <v>18</v>
+      </c>
+      <c r="F977">
+        <v>9</v>
+      </c>
+      <c r="G977">
+        <v>27</v>
+      </c>
+      <c r="I977" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="978" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A978" t="s">
+        <v>57</v>
+      </c>
+      <c r="B978" t="s">
+        <v>53</v>
+      </c>
+      <c r="C978">
+        <v>2026</v>
+      </c>
+      <c r="D978">
+        <v>2026</v>
+      </c>
+      <c r="E978">
+        <v>18</v>
+      </c>
+      <c r="F978">
+        <v>9</v>
+      </c>
+      <c r="G978">
+        <v>27</v>
+      </c>
+      <c r="I978" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="979" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A979" t="s">
+        <v>57</v>
+      </c>
+      <c r="B979" t="s">
+        <v>54</v>
+      </c>
+      <c r="C979">
+        <v>2026</v>
+      </c>
+      <c r="D979">
+        <v>2026</v>
+      </c>
+      <c r="E979">
+        <v>18</v>
+      </c>
+      <c r="F979">
+        <v>9</v>
+      </c>
+      <c r="G979">
+        <v>27</v>
+      </c>
+      <c r="I979" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="980" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A980" t="s">
+        <v>57</v>
+      </c>
+      <c r="B980" t="s">
+        <v>55</v>
+      </c>
+      <c r="C980">
+        <v>2026</v>
+      </c>
+      <c r="D980">
+        <v>2026</v>
+      </c>
+      <c r="E980">
+        <v>12</v>
+      </c>
+      <c r="F980">
+        <v>15</v>
+      </c>
+      <c r="G980">
+        <v>27</v>
+      </c>
+      <c r="I980" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="981" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A981" t="s">
+        <v>74</v>
+      </c>
+      <c r="B981" t="s">
+        <v>2</v>
+      </c>
+      <c r="C981">
+        <v>2026</v>
+      </c>
+      <c r="D981">
+        <v>2026</v>
+      </c>
+      <c r="E981">
+        <v>0</v>
+      </c>
+      <c r="F981">
+        <v>9</v>
+      </c>
+      <c r="G981">
+        <v>9</v>
+      </c>
+      <c r="I981" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="982" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A982" t="s">
+        <v>74</v>
+      </c>
+      <c r="B982" t="s">
+        <v>3</v>
+      </c>
+      <c r="C982">
+        <v>2026</v>
+      </c>
+      <c r="D982">
+        <v>2026</v>
+      </c>
+      <c r="E982">
+        <v>0</v>
+      </c>
+      <c r="F982">
+        <v>9</v>
+      </c>
+      <c r="G982">
+        <v>9</v>
+      </c>
+      <c r="I982" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="983" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A983" t="s">
+        <v>74</v>
+      </c>
+      <c r="B983" t="s">
+        <v>35</v>
+      </c>
+      <c r="C983">
+        <v>2026</v>
+      </c>
+      <c r="D983">
+        <v>2026</v>
+      </c>
+      <c r="E983">
+        <v>0</v>
+      </c>
+      <c r="F983">
+        <v>9</v>
+      </c>
+      <c r="G983">
+        <v>9</v>
+      </c>
+      <c r="I983" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="984" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A984" t="s">
+        <v>74</v>
+      </c>
+      <c r="B984" t="s">
+        <v>4</v>
+      </c>
+      <c r="C984">
+        <v>2026</v>
+      </c>
+      <c r="D984">
+        <v>2026</v>
+      </c>
+      <c r="E984">
+        <v>0</v>
+      </c>
+      <c r="F984">
+        <v>9</v>
+      </c>
+      <c r="G984">
+        <v>9</v>
+      </c>
+      <c r="I984" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="985" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A985" t="s">
+        <v>74</v>
+      </c>
+      <c r="B985" t="s">
+        <v>5</v>
+      </c>
+      <c r="C985">
+        <v>2026</v>
+      </c>
+      <c r="D985">
+        <v>2026</v>
+      </c>
+      <c r="E985">
+        <v>0</v>
+      </c>
+      <c r="F985">
+        <v>9</v>
+      </c>
+      <c r="G985">
+        <v>9</v>
+      </c>
+      <c r="I985" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="986" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A986" t="s">
+        <v>74</v>
+      </c>
+      <c r="B986" t="s">
+        <v>6</v>
+      </c>
+      <c r="C986">
+        <v>2026</v>
+      </c>
+      <c r="D986">
+        <v>2026</v>
+      </c>
+      <c r="E986">
+        <v>0</v>
+      </c>
+      <c r="F986">
+        <v>9</v>
+      </c>
+      <c r="G986">
+        <v>9</v>
+      </c>
+      <c r="I986" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="987" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A987" t="s">
+        <v>74</v>
+      </c>
+      <c r="B987" t="s">
+        <v>40</v>
+      </c>
+      <c r="C987">
+        <v>2026</v>
+      </c>
+      <c r="D987">
+        <v>2026</v>
+      </c>
+      <c r="E987">
+        <v>0</v>
+      </c>
+      <c r="F987">
+        <v>9</v>
+      </c>
+      <c r="G987">
+        <v>9</v>
+      </c>
+      <c r="I987" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="988" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A988" t="s">
+        <v>74</v>
+      </c>
+      <c r="B988" t="s">
+        <v>7</v>
+      </c>
+      <c r="C988">
+        <v>2026</v>
+      </c>
+      <c r="D988">
+        <v>2026</v>
+      </c>
+      <c r="E988">
+        <v>0</v>
+      </c>
+      <c r="F988">
+        <v>9</v>
+      </c>
+      <c r="G988">
+        <v>9</v>
+      </c>
+      <c r="I988" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="989" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A989" t="s">
+        <v>74</v>
+      </c>
+      <c r="B989" t="s">
+        <v>8</v>
+      </c>
+      <c r="C989">
+        <v>2026</v>
+      </c>
+      <c r="D989">
+        <v>2026</v>
+      </c>
+      <c r="E989">
+        <v>0</v>
+      </c>
+      <c r="F989">
+        <v>9</v>
+      </c>
+      <c r="G989">
+        <v>9</v>
+      </c>
+      <c r="I989" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="990" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A990" t="s">
+        <v>74</v>
+      </c>
+      <c r="B990" t="s">
+        <v>9</v>
+      </c>
+      <c r="C990">
+        <v>2026</v>
+      </c>
+      <c r="D990">
+        <v>2026</v>
+      </c>
+      <c r="E990">
+        <v>0</v>
+      </c>
+      <c r="F990">
+        <v>9</v>
+      </c>
+      <c r="G990">
+        <v>9</v>
+      </c>
+      <c r="I990" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="991" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A991" t="s">
+        <v>74</v>
+      </c>
+      <c r="B991" t="s">
+        <v>31</v>
+      </c>
+      <c r="C991">
+        <v>2026</v>
+      </c>
+      <c r="D991">
+        <v>2026</v>
+      </c>
+      <c r="E991">
+        <v>0</v>
+      </c>
+      <c r="F991">
+        <v>9</v>
+      </c>
+      <c r="G991">
+        <v>9</v>
+      </c>
+      <c r="I991" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="992" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A992" t="s">
+        <v>74</v>
+      </c>
+      <c r="B992" t="s">
+        <v>32</v>
+      </c>
+      <c r="C992">
+        <v>2026</v>
+      </c>
+      <c r="D992">
+        <v>2026</v>
+      </c>
+      <c r="E992">
+        <v>0</v>
+      </c>
+      <c r="F992">
+        <v>9</v>
+      </c>
+      <c r="G992">
+        <v>9</v>
+      </c>
+      <c r="I992" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="993" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A993" t="s">
+        <v>74</v>
+      </c>
+      <c r="B993" t="s">
+        <v>10</v>
+      </c>
+      <c r="C993">
+        <v>2026</v>
+      </c>
+      <c r="D993">
+        <v>2026</v>
+      </c>
+      <c r="E993">
+        <v>0</v>
+      </c>
+      <c r="F993">
+        <v>9</v>
+      </c>
+      <c r="G993">
+        <v>9</v>
+      </c>
+      <c r="I993" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="994" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A994" t="s">
+        <v>74</v>
+      </c>
+      <c r="B994" t="s">
+        <v>11</v>
+      </c>
+      <c r="C994">
+        <v>2026</v>
+      </c>
+      <c r="D994">
+        <v>2026</v>
+      </c>
+      <c r="E994">
+        <v>0</v>
+      </c>
+      <c r="F994">
+        <v>9</v>
+      </c>
+      <c r="G994">
+        <v>9</v>
+      </c>
+      <c r="I994" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="995" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A995" t="s">
+        <v>74</v>
+      </c>
+      <c r="B995" t="s">
+        <v>12</v>
+      </c>
+      <c r="C995">
+        <v>2026</v>
+      </c>
+      <c r="D995">
+        <v>2026</v>
+      </c>
+      <c r="E995">
+        <v>0</v>
+      </c>
+      <c r="F995">
+        <v>9</v>
+      </c>
+      <c r="G995">
+        <v>9</v>
+      </c>
+      <c r="I995" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="996" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A996" t="s">
+        <v>74</v>
+      </c>
+      <c r="B996" t="s">
+        <v>13</v>
+      </c>
+      <c r="C996">
+        <v>2026</v>
+      </c>
+      <c r="D996">
+        <v>2026</v>
+      </c>
+      <c r="E996">
+        <v>0</v>
+      </c>
+      <c r="F996">
+        <v>9</v>
+      </c>
+      <c r="G996">
+        <v>9</v>
+      </c>
+      <c r="I996" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="997" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A997" t="s">
+        <v>74</v>
+      </c>
+      <c r="B997" t="s">
+        <v>29</v>
+      </c>
+      <c r="C997">
+        <v>2026</v>
+      </c>
+      <c r="D997">
+        <v>2026</v>
+      </c>
+      <c r="E997">
+        <v>0</v>
+      </c>
+      <c r="F997">
+        <v>9</v>
+      </c>
+      <c r="G997">
+        <v>9</v>
+      </c>
+      <c r="I997" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="998" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A998" t="s">
+        <v>74</v>
+      </c>
+      <c r="B998" t="s">
+        <v>28</v>
+      </c>
+      <c r="C998">
+        <v>2026</v>
+      </c>
+      <c r="D998">
+        <v>2026</v>
+      </c>
+      <c r="E998">
+        <v>0</v>
+      </c>
+      <c r="F998">
+        <v>9</v>
+      </c>
+      <c r="G998">
+        <v>9</v>
+      </c>
+      <c r="I998" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="999" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A999" t="s">
+        <v>74</v>
+      </c>
+      <c r="B999" t="s">
+        <v>14</v>
+      </c>
+      <c r="C999">
+        <v>2026</v>
+      </c>
+      <c r="D999">
+        <v>2026</v>
+      </c>
+      <c r="E999">
+        <v>0</v>
+      </c>
+      <c r="F999">
+        <v>9</v>
+      </c>
+      <c r="G999">
+        <v>9</v>
+      </c>
+      <c r="I999" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1000" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1000">
+        <v>2026</v>
+      </c>
+      <c r="D1000">
+        <v>2026</v>
+      </c>
+      <c r="E1000">
+        <v>0</v>
+      </c>
+      <c r="F1000">
+        <v>9</v>
+      </c>
+      <c r="G1000">
+        <v>9</v>
+      </c>
+      <c r="I1000" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1001" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1001">
+        <v>2026</v>
+      </c>
+      <c r="D1001">
+        <v>2026</v>
+      </c>
+      <c r="E1001">
+        <v>0</v>
+      </c>
+      <c r="F1001">
+        <v>9</v>
+      </c>
+      <c r="G1001">
+        <v>9</v>
+      </c>
+      <c r="I1001" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1002" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1002">
+        <v>2026</v>
+      </c>
+      <c r="D1002">
+        <v>2026</v>
+      </c>
+      <c r="E1002">
+        <v>0</v>
+      </c>
+      <c r="F1002">
+        <v>9</v>
+      </c>
+      <c r="G1002">
+        <v>9</v>
+      </c>
+      <c r="I1002" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1003" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1003">
+        <v>2026</v>
+      </c>
+      <c r="D1003">
+        <v>2026</v>
+      </c>
+      <c r="E1003">
+        <v>0</v>
+      </c>
+      <c r="F1003">
+        <v>9</v>
+      </c>
+      <c r="G1003">
+        <v>9</v>
+      </c>
+      <c r="I1003" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1004" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1004">
+        <v>2026</v>
+      </c>
+      <c r="D1004">
+        <v>2026</v>
+      </c>
+      <c r="E1004">
+        <v>0</v>
+      </c>
+      <c r="F1004">
+        <v>9</v>
+      </c>
+      <c r="G1004">
+        <v>9</v>
+      </c>
+      <c r="I1004" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1005" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1005">
+        <v>2026</v>
+      </c>
+      <c r="D1005">
+        <v>2026</v>
+      </c>
+      <c r="E1005">
+        <v>0</v>
+      </c>
+      <c r="F1005">
+        <v>9</v>
+      </c>
+      <c r="G1005">
+        <v>9</v>
+      </c>
+      <c r="I1005" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1006" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1006">
+        <v>2026</v>
+      </c>
+      <c r="D1006">
+        <v>2026</v>
+      </c>
+      <c r="E1006">
+        <v>0</v>
+      </c>
+      <c r="F1006">
+        <v>9</v>
+      </c>
+      <c r="G1006">
+        <v>9</v>
+      </c>
+      <c r="I1006" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1007" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1007">
+        <v>2026</v>
+      </c>
+      <c r="D1007">
+        <v>2026</v>
+      </c>
+      <c r="E1007">
+        <v>0</v>
+      </c>
+      <c r="F1007">
+        <v>9</v>
+      </c>
+      <c r="G1007">
+        <v>9</v>
+      </c>
+      <c r="I1007" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1008" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1008">
+        <v>2026</v>
+      </c>
+      <c r="D1008">
+        <v>2026</v>
+      </c>
+      <c r="E1008">
+        <v>0</v>
+      </c>
+      <c r="F1008">
+        <v>9</v>
+      </c>
+      <c r="G1008">
+        <v>9</v>
+      </c>
+      <c r="I1008" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1009" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1009">
+        <v>2026</v>
+      </c>
+      <c r="D1009">
+        <v>2026</v>
+      </c>
+      <c r="E1009">
+        <v>0</v>
+      </c>
+      <c r="F1009">
+        <v>9</v>
+      </c>
+      <c r="G1009">
+        <v>9</v>
+      </c>
+      <c r="I1009" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1010" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1010">
+        <v>2026</v>
+      </c>
+      <c r="D1010">
+        <v>2026</v>
+      </c>
+      <c r="E1010">
+        <v>0</v>
+      </c>
+      <c r="F1010">
+        <v>9</v>
+      </c>
+      <c r="G1010">
+        <v>9</v>
+      </c>
+      <c r="I1010" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1011" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1011">
+        <v>2026</v>
+      </c>
+      <c r="D1011">
+        <v>2026</v>
+      </c>
+      <c r="E1011">
+        <v>0</v>
+      </c>
+      <c r="F1011">
+        <v>9</v>
+      </c>
+      <c r="G1011">
+        <v>9</v>
+      </c>
+      <c r="I1011" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1012" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1012">
+        <v>2026</v>
+      </c>
+      <c r="D1012">
+        <v>2026</v>
+      </c>
+      <c r="E1012">
+        <v>0</v>
+      </c>
+      <c r="F1012">
+        <v>9</v>
+      </c>
+      <c r="G1012">
+        <v>9</v>
+      </c>
+      <c r="I1012" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1013" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1013">
+        <v>2026</v>
+      </c>
+      <c r="D1013">
+        <v>2026</v>
+      </c>
+      <c r="E1013">
+        <v>0</v>
+      </c>
+      <c r="F1013">
+        <v>9</v>
+      </c>
+      <c r="G1013">
+        <v>9</v>
+      </c>
+      <c r="I1013" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1014" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1014">
+        <v>2026</v>
+      </c>
+      <c r="D1014">
+        <v>2026</v>
+      </c>
+      <c r="E1014">
+        <v>0</v>
+      </c>
+      <c r="F1014">
+        <v>9</v>
+      </c>
+      <c r="G1014">
+        <v>9</v>
+      </c>
+      <c r="I1014" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1015" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1015">
+        <v>2026</v>
+      </c>
+      <c r="D1015">
+        <v>2026</v>
+      </c>
+      <c r="E1015">
+        <v>0</v>
+      </c>
+      <c r="F1015">
+        <v>9</v>
+      </c>
+      <c r="G1015">
+        <v>9</v>
+      </c>
+      <c r="I1015" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1016" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1016">
+        <v>2026</v>
+      </c>
+      <c r="D1016">
+        <v>2026</v>
+      </c>
+      <c r="E1016">
+        <v>0</v>
+      </c>
+      <c r="F1016">
+        <v>9</v>
+      </c>
+      <c r="G1016">
+        <v>9</v>
+      </c>
+      <c r="I1016" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1017" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1017">
+        <v>2026</v>
+      </c>
+      <c r="D1017">
+        <v>2026</v>
+      </c>
+      <c r="E1017">
+        <v>0</v>
+      </c>
+      <c r="F1017">
+        <v>9</v>
+      </c>
+      <c r="G1017">
+        <v>9</v>
+      </c>
+      <c r="I1017" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1018" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1018">
+        <v>2026</v>
+      </c>
+      <c r="D1018">
+        <v>2026</v>
+      </c>
+      <c r="E1018">
+        <v>0</v>
+      </c>
+      <c r="F1018">
+        <v>9</v>
+      </c>
+      <c r="G1018">
+        <v>9</v>
+      </c>
+      <c r="I1018" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1019" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1019">
+        <v>2026</v>
+      </c>
+      <c r="D1019">
+        <v>2026</v>
+      </c>
+      <c r="E1019">
+        <v>0</v>
+      </c>
+      <c r="F1019">
+        <v>9</v>
+      </c>
+      <c r="G1019">
+        <v>9</v>
+      </c>
+      <c r="I1019" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1020" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1020">
+        <v>2026</v>
+      </c>
+      <c r="D1020">
+        <v>2026</v>
+      </c>
+      <c r="E1020">
+        <v>0</v>
+      </c>
+      <c r="F1020">
+        <v>9</v>
+      </c>
+      <c r="G1020">
+        <v>9</v>
+      </c>
+      <c r="I1020" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1021" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1021">
+        <v>2026</v>
+      </c>
+      <c r="D1021">
+        <v>2026</v>
+      </c>
+      <c r="E1021">
+        <v>0</v>
+      </c>
+      <c r="F1021">
+        <v>9</v>
+      </c>
+      <c r="G1021">
+        <v>9</v>
+      </c>
+      <c r="I1021" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1022" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1022">
+        <v>2026</v>
+      </c>
+      <c r="D1022">
+        <v>2026</v>
+      </c>
+      <c r="E1022">
+        <v>0</v>
+      </c>
+      <c r="F1022">
+        <v>9</v>
+      </c>
+      <c r="G1022">
+        <v>9</v>
+      </c>
+      <c r="I1022" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1023" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1023">
+        <v>2026</v>
+      </c>
+      <c r="D1023">
+        <v>2026</v>
+      </c>
+      <c r="E1023">
+        <v>0</v>
+      </c>
+      <c r="F1023">
+        <v>9</v>
+      </c>
+      <c r="G1023">
+        <v>9</v>
+      </c>
+      <c r="I1023" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1024" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1024">
+        <v>2026</v>
+      </c>
+      <c r="D1024">
+        <v>2026</v>
+      </c>
+      <c r="E1024">
+        <v>0</v>
+      </c>
+      <c r="F1024">
+        <v>9</v>
+      </c>
+      <c r="G1024">
+        <v>9</v>
+      </c>
+      <c r="I1024" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1025" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1025">
+        <v>2026</v>
+      </c>
+      <c r="D1025">
+        <v>2026</v>
+      </c>
+      <c r="E1025">
+        <v>0</v>
+      </c>
+      <c r="F1025">
+        <v>9</v>
+      </c>
+      <c r="G1025">
+        <v>9</v>
+      </c>
+      <c r="I1025" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1026" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1026">
+        <v>2026</v>
+      </c>
+      <c r="D1026">
+        <v>2026</v>
+      </c>
+      <c r="E1026">
+        <v>0</v>
+      </c>
+      <c r="F1026">
+        <v>9</v>
+      </c>
+      <c r="G1026">
+        <v>9</v>
+      </c>
+      <c r="I1026" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1027" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1027">
+        <v>2026</v>
+      </c>
+      <c r="D1027">
+        <v>2026</v>
+      </c>
+      <c r="E1027">
+        <v>0</v>
+      </c>
+      <c r="F1027">
+        <v>9</v>
+      </c>
+      <c r="G1027">
+        <v>9</v>
+      </c>
+      <c r="I1027" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1028" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1028">
+        <v>2026</v>
+      </c>
+      <c r="D1028">
+        <v>2026</v>
+      </c>
+      <c r="E1028">
+        <v>0</v>
+      </c>
+      <c r="F1028">
+        <v>9</v>
+      </c>
+      <c r="G1028">
+        <v>9</v>
+      </c>
+      <c r="I1028" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1029" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1029">
+        <v>2026</v>
+      </c>
+      <c r="D1029">
+        <v>2026</v>
+      </c>
+      <c r="E1029">
+        <v>0</v>
+      </c>
+      <c r="F1029">
+        <v>9</v>
+      </c>
+      <c r="G1029">
+        <v>9</v>
+      </c>
+      <c r="I1029" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1030" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1030">
+        <v>2026</v>
+      </c>
+      <c r="D1030">
+        <v>2026</v>
+      </c>
+      <c r="E1030">
+        <v>0</v>
+      </c>
+      <c r="F1030">
+        <v>9</v>
+      </c>
+      <c r="G1030">
+        <v>9</v>
+      </c>
+      <c r="I1030" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1031" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1031">
+        <v>2026</v>
+      </c>
+      <c r="D1031">
+        <v>2026</v>
+      </c>
+      <c r="E1031">
+        <v>0</v>
+      </c>
+      <c r="F1031">
+        <v>9</v>
+      </c>
+      <c r="G1031">
+        <v>9</v>
+      </c>
+      <c r="I1031" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1032" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1032">
+        <v>2026</v>
+      </c>
+      <c r="D1032">
+        <v>2026</v>
+      </c>
+      <c r="E1032">
+        <v>0</v>
+      </c>
+      <c r="F1032">
+        <v>9</v>
+      </c>
+      <c r="G1032">
+        <v>9</v>
+      </c>
+      <c r="I1032" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1033" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1033">
+        <v>2026</v>
+      </c>
+      <c r="D1033">
+        <v>2026</v>
+      </c>
+      <c r="E1033">
+        <v>0</v>
+      </c>
+      <c r="F1033">
+        <v>9</v>
+      </c>
+      <c r="G1033">
+        <v>9</v>
+      </c>
+      <c r="I1033" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1034" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1034">
+        <v>2026</v>
+      </c>
+      <c r="D1034">
+        <v>2026</v>
+      </c>
+      <c r="E1034">
+        <v>0</v>
+      </c>
+      <c r="F1034">
+        <v>9</v>
+      </c>
+      <c r="G1034">
+        <v>9</v>
+      </c>
+      <c r="I1034" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1035" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1035">
+        <v>2026</v>
+      </c>
+      <c r="D1035">
+        <v>2026</v>
+      </c>
+      <c r="E1035">
+        <v>0</v>
+      </c>
+      <c r="F1035">
+        <v>9</v>
+      </c>
+      <c r="G1035">
+        <v>9</v>
+      </c>
+      <c r="I1035" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1036" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1036">
+        <v>2026</v>
+      </c>
+      <c r="D1036">
+        <v>2026</v>
+      </c>
+      <c r="E1036">
+        <v>0</v>
+      </c>
+      <c r="F1036">
+        <v>9</v>
+      </c>
+      <c r="G1036">
+        <v>9</v>
+      </c>
+      <c r="I1036" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
